--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1792,6 +1792,2759 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123249496</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Överstmossen, Överstmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>588070</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6634198</v>
+      </c>
+      <c r="S12" t="n">
+        <v>9</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123250725</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Överstmossen, Överstmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>588146</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6634204</v>
+      </c>
+      <c r="S13" t="n">
+        <v>6</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123247723</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>587819</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6634164</v>
+      </c>
+      <c r="S14" t="n">
+        <v>6</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123249452</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Överstmossen, Överstmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>588053</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6634200</v>
+      </c>
+      <c r="S15" t="n">
+        <v>7</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123250437</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Överstmossen, Överstmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>588103</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6634221</v>
+      </c>
+      <c r="S16" t="n">
+        <v>7</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123250354</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Överstmossen, Överstmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>588099</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6634227</v>
+      </c>
+      <c r="S17" t="n">
+        <v>8</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123250520</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Överstmossen, Överstmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>588123</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6634219</v>
+      </c>
+      <c r="S18" t="n">
+        <v>7</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123248138</v>
+      </c>
+      <c r="B19" t="n">
+        <v>105471</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>587888</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6634183</v>
+      </c>
+      <c r="S19" t="n">
+        <v>8</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>123248683</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>587942</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6634200</v>
+      </c>
+      <c r="S20" t="n">
+        <v>8</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>123248025</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>587890</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6634184</v>
+      </c>
+      <c r="S21" t="n">
+        <v>6</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>123251441</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Överstmossen, Överstmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>588163</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6634261</v>
+      </c>
+      <c r="S22" t="n">
+        <v>8</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>123251808</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>587915</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6634215</v>
+      </c>
+      <c r="S23" t="n">
+        <v>9</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>123249194</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>587963</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6634186</v>
+      </c>
+      <c r="S24" t="n">
+        <v>7</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>123251549</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Överstmossen, Överstmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>588114</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6634233</v>
+      </c>
+      <c r="S25" t="n">
+        <v>7</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>123249094</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>587959</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6634188</v>
+      </c>
+      <c r="S26" t="n">
+        <v>7</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>123248542</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kivsta, Kila sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>587933</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6634187</v>
+      </c>
+      <c r="S27" t="n">
+        <v>9</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>123251464</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Överstmossen, Överstmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>588142</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6634249</v>
+      </c>
+      <c r="S28" t="n">
+        <v>8</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>123249372</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Överstmossen, Överstmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>588038</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6634200</v>
+      </c>
+      <c r="S29" t="n">
+        <v>8</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>123247980</v>
+      </c>
+      <c r="B30" t="n">
+        <v>105471</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>587889</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6634188</v>
+      </c>
+      <c r="S30" t="n">
+        <v>8</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>123251389</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Överstmossen, Överstmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>588189</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6634246</v>
+      </c>
+      <c r="S31" t="n">
+        <v>6</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>123250606</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Överstmossen, Överstmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>588109</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6634191</v>
+      </c>
+      <c r="S32" t="n">
+        <v>9</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2430,10 +2430,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123250354</v>
+        <v>123248138</v>
       </c>
       <c r="B17" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2442,30 +2442,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2480,14 +2480,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>588099</v>
+        <v>587888</v>
       </c>
       <c r="R17" t="n">
-        <v>6634227</v>
+        <v>6634183</v>
       </c>
       <c r="S17" t="n">
         <v>8</v>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2561,7 +2561,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123250520</v>
+        <v>123248683</v>
       </c>
       <c r="B18" t="n">
         <v>98365</v>
@@ -2596,12 +2596,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2611,17 +2611,17 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>588123</v>
+        <v>587942</v>
       </c>
       <c r="R18" t="n">
-        <v>6634219</v>
+        <v>6634200</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2692,10 +2692,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123248138</v>
+        <v>123250354</v>
       </c>
       <c r="B19" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2704,30 +2704,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2742,14 +2742,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587888</v>
+        <v>588099</v>
       </c>
       <c r="R19" t="n">
-        <v>6634183</v>
+        <v>6634227</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2823,7 +2823,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123248683</v>
+        <v>123250520</v>
       </c>
       <c r="B20" t="n">
         <v>98365</v>
@@ -2858,12 +2858,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2873,17 +2873,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>587942</v>
+        <v>588123</v>
       </c>
       <c r="R20" t="n">
-        <v>6634200</v>
+        <v>6634219</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -4013,7 +4013,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123249372</v>
+        <v>123251389</v>
       </c>
       <c r="B29" t="n">
         <v>98365</v>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4067,13 +4067,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>588038</v>
+        <v>588189</v>
       </c>
       <c r="R29" t="n">
-        <v>6634200</v>
+        <v>6634246</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4144,10 +4144,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123247980</v>
+        <v>123249372</v>
       </c>
       <c r="B30" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4156,35 +4156,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -4194,14 +4194,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587889</v>
+        <v>588038</v>
       </c>
       <c r="R30" t="n">
-        <v>6634188</v>
+        <v>6634200</v>
       </c>
       <c r="S30" t="n">
         <v>8</v>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4258,16 +4258,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Mark/jord på land</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4285,10 +4275,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123251389</v>
+        <v>123247980</v>
       </c>
       <c r="B31" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4297,35 +4287,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4335,17 +4325,17 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>588189</v>
+        <v>587889</v>
       </c>
       <c r="R31" t="n">
-        <v>6634246</v>
+        <v>6634188</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4374,7 +4364,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4384,7 +4374,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4399,6 +4389,16 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4545,6 +4545,137 @@
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>123251336</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Överstmossen, Överstmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>588190</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6634249</v>
+      </c>
+      <c r="S33" t="n">
+        <v>8</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1794,7 +1794,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123249496</v>
+        <v>123248025</v>
       </c>
       <c r="B12" t="n">
         <v>98365</v>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1844,17 +1844,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588070</v>
+        <v>587890</v>
       </c>
       <c r="R12" t="n">
-        <v>6634198</v>
+        <v>6634184</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2056,7 +2056,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123247723</v>
+        <v>123251389</v>
       </c>
       <c r="B14" t="n">
         <v>98365</v>
@@ -2089,17 +2089,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>587819</v>
+        <v>588189</v>
       </c>
       <c r="R14" t="n">
-        <v>6634164</v>
+        <v>6634246</v>
       </c>
       <c r="S14" t="n">
         <v>6</v>
@@ -2131,7 +2145,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2141,7 +2155,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2152,6 +2166,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2299,7 +2318,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123250437</v>
+        <v>123249372</v>
       </c>
       <c r="B16" t="n">
         <v>98365</v>
@@ -2334,7 +2353,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2353,13 +2372,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>588103</v>
+        <v>588038</v>
       </c>
       <c r="R16" t="n">
-        <v>6634221</v>
+        <v>6634200</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2388,7 +2407,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2398,7 +2417,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2430,10 +2449,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123248138</v>
+        <v>123250437</v>
       </c>
       <c r="B17" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2442,25 +2461,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2470,7 +2489,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2480,17 +2499,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587888</v>
+        <v>588103</v>
       </c>
       <c r="R17" t="n">
-        <v>6634183</v>
+        <v>6634221</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2519,7 +2538,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2529,7 +2548,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2561,7 +2580,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123248683</v>
+        <v>123251808</v>
       </c>
       <c r="B18" t="n">
         <v>98365</v>
@@ -2596,12 +2615,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2615,13 +2634,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587942</v>
+        <v>587915</v>
       </c>
       <c r="R18" t="n">
-        <v>6634200</v>
+        <v>6634215</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2650,7 +2669,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2660,7 +2679,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2692,7 +2711,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123250354</v>
+        <v>123250520</v>
       </c>
       <c r="B19" t="n">
         <v>98365</v>
@@ -2727,7 +2746,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2746,13 +2765,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>588099</v>
+        <v>588123</v>
       </c>
       <c r="R19" t="n">
-        <v>6634227</v>
+        <v>6634219</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2781,7 +2800,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2791,7 +2810,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2823,7 +2842,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123250520</v>
+        <v>123251464</v>
       </c>
       <c r="B20" t="n">
         <v>98365</v>
@@ -2877,13 +2896,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>588123</v>
+        <v>588142</v>
       </c>
       <c r="R20" t="n">
-        <v>6634219</v>
+        <v>6634249</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2912,7 +2931,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2922,7 +2941,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2954,7 +2973,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123248025</v>
+        <v>123248683</v>
       </c>
       <c r="B21" t="n">
         <v>98365</v>
@@ -2989,12 +3008,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3008,13 +3027,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>587890</v>
+        <v>587942</v>
       </c>
       <c r="R21" t="n">
-        <v>6634184</v>
+        <v>6634200</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3043,7 +3062,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3053,7 +3072,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3085,10 +3104,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123251441</v>
+        <v>123248542</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3097,55 +3116,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Kivsta, Kila sn, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>588163</v>
+        <v>587933</v>
       </c>
       <c r="R22" t="n">
-        <v>6634261</v>
+        <v>6634187</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3174,7 +3184,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3184,7 +3194,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3199,6 +3209,26 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3216,7 +3246,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123251808</v>
+        <v>123249496</v>
       </c>
       <c r="B23" t="n">
         <v>98365</v>
@@ -3251,12 +3281,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3266,14 +3296,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587915</v>
+        <v>588070</v>
       </c>
       <c r="R23" t="n">
-        <v>6634215</v>
+        <v>6634198</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3305,7 +3335,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3315,7 +3345,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3347,7 +3377,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123249194</v>
+        <v>123250606</v>
       </c>
       <c r="B24" t="n">
         <v>98365</v>
@@ -3382,7 +3412,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3397,17 +3427,17 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587963</v>
+        <v>588109</v>
       </c>
       <c r="R24" t="n">
-        <v>6634186</v>
+        <v>6634191</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3436,7 +3466,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3446,7 +3476,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3478,7 +3508,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123251549</v>
+        <v>123250354</v>
       </c>
       <c r="B25" t="n">
         <v>98365</v>
@@ -3513,7 +3543,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3532,13 +3562,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>588114</v>
+        <v>588099</v>
       </c>
       <c r="R25" t="n">
-        <v>6634233</v>
+        <v>6634227</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3567,7 +3597,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3577,7 +3607,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3609,7 +3639,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123249094</v>
+        <v>123251549</v>
       </c>
       <c r="B26" t="n">
         <v>98365</v>
@@ -3644,12 +3674,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3659,14 +3689,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587959</v>
+        <v>588114</v>
       </c>
       <c r="R26" t="n">
-        <v>6634188</v>
+        <v>6634233</v>
       </c>
       <c r="S26" t="n">
         <v>7</v>
@@ -3698,7 +3728,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3708,7 +3738,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3740,10 +3770,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123248542</v>
+        <v>123249094</v>
       </c>
       <c r="B27" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3752,46 +3782,55 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kivsta, Kila sn, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>587933</v>
+        <v>587959</v>
       </c>
       <c r="R27" t="n">
-        <v>6634187</v>
+        <v>6634188</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3820,7 +3859,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3830,7 +3869,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3845,26 +3884,6 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3882,7 +3901,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123251464</v>
+        <v>123251441</v>
       </c>
       <c r="B28" t="n">
         <v>98365</v>
@@ -3917,12 +3936,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3936,10 +3955,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588142</v>
+        <v>588163</v>
       </c>
       <c r="R28" t="n">
-        <v>6634249</v>
+        <v>6634261</v>
       </c>
       <c r="S28" t="n">
         <v>8</v>
@@ -3971,7 +3990,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3981,7 +4000,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4013,7 +4032,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123251389</v>
+        <v>123249194</v>
       </c>
       <c r="B29" t="n">
         <v>98365</v>
@@ -4048,12 +4067,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -4063,17 +4082,17 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>588189</v>
+        <v>587963</v>
       </c>
       <c r="R29" t="n">
-        <v>6634246</v>
+        <v>6634186</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4102,7 +4121,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4112,7 +4131,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4144,10 +4163,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123249372</v>
+        <v>123248138</v>
       </c>
       <c r="B30" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4156,35 +4175,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -4194,14 +4213,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>588038</v>
+        <v>587888</v>
       </c>
       <c r="R30" t="n">
-        <v>6634200</v>
+        <v>6634183</v>
       </c>
       <c r="S30" t="n">
         <v>8</v>
@@ -4233,7 +4252,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4243,7 +4262,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4275,10 +4294,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123247980</v>
+        <v>123247723</v>
       </c>
       <c r="B31" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4287,55 +4306,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>587889</v>
+        <v>587819</v>
       </c>
       <c r="R31" t="n">
-        <v>6634188</v>
+        <v>6634164</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4364,7 +4369,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4374,7 +4379,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4385,21 +4390,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Mark/jord på land</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Ground/soil on land</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4416,10 +4406,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123250606</v>
+        <v>123247980</v>
       </c>
       <c r="B32" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4428,30 +4418,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4466,17 +4456,17 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>588109</v>
+        <v>587889</v>
       </c>
       <c r="R32" t="n">
-        <v>6634191</v>
+        <v>6634188</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4505,7 +4495,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4515,7 +4505,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4530,6 +4520,16 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4676,6 +4676,1271 @@
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>123284690</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>O Kivsta, Vstm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>588177</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6634223</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>123284697</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>O Kivsta, Vstm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>587914</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6634236</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>123284698</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>O Kivsta, Vstm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>587922</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6634202</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>123284692</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>O Kivsta, Vstm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>588131</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6634212</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>123284696</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>O Kivsta, Vstm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>587970</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6634188</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>123284693</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>O Kivsta, Vstm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>588083</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6634204</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>123284689</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>O Kivsta, Vstm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>588176</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6634236</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>123284694</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>O Kivsta, Vstm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>588076</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6634215</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>123295534</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>O Kivsta, Vstm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>588070</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6634240</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>123284695</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>O Kivsta, Vstm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>588072</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6634226</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>123284688</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>O Kivsta, Vstm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>588044</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6634206</v>
+      </c>
+      <c r="S44" t="n">
+        <v>15</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -1794,7 +1794,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123248025</v>
+        <v>123251012</v>
       </c>
       <c r="B12" t="n">
         <v>98365</v>
@@ -1829,12 +1829,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587890</v>
+        <v>588146</v>
       </c>
       <c r="R12" t="n">
-        <v>6634184</v>
+        <v>6634204</v>
       </c>
       <c r="S12" t="n">
         <v>6</v>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1925,7 +1925,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123250725</v>
+        <v>123250437</v>
       </c>
       <c r="B13" t="n">
         <v>98365</v>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1979,13 +1979,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588146</v>
+        <v>588103</v>
       </c>
       <c r="R13" t="n">
-        <v>6634204</v>
+        <v>6634221</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2056,10 +2056,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123251389</v>
+        <v>123247980</v>
       </c>
       <c r="B14" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2068,35 +2068,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2106,17 +2106,17 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588189</v>
+        <v>587889</v>
       </c>
       <c r="R14" t="n">
-        <v>6634246</v>
+        <v>6634188</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,6 +2170,16 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2187,7 +2197,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123249452</v>
+        <v>123251389</v>
       </c>
       <c r="B15" t="n">
         <v>98365</v>
@@ -2222,12 +2232,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2241,13 +2251,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>588053</v>
+        <v>588189</v>
       </c>
       <c r="R15" t="n">
-        <v>6634200</v>
+        <v>6634246</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2276,7 +2286,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2286,7 +2296,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2318,7 +2328,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123249372</v>
+        <v>123251441</v>
       </c>
       <c r="B16" t="n">
         <v>98365</v>
@@ -2353,7 +2363,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2372,10 +2382,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>588038</v>
+        <v>588163</v>
       </c>
       <c r="R16" t="n">
-        <v>6634200</v>
+        <v>6634261</v>
       </c>
       <c r="S16" t="n">
         <v>8</v>
@@ -2407,7 +2417,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2417,7 +2427,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2449,7 +2459,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123250437</v>
+        <v>123248025</v>
       </c>
       <c r="B17" t="n">
         <v>98365</v>
@@ -2484,12 +2494,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2499,17 +2509,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>588103</v>
+        <v>587890</v>
       </c>
       <c r="R17" t="n">
-        <v>6634221</v>
+        <v>6634184</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2538,7 +2548,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2548,7 +2558,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2580,7 +2590,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123251808</v>
+        <v>123249496</v>
       </c>
       <c r="B18" t="n">
         <v>98365</v>
@@ -2615,12 +2625,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2630,14 +2640,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587915</v>
+        <v>588070</v>
       </c>
       <c r="R18" t="n">
-        <v>6634215</v>
+        <v>6634198</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2669,7 +2679,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2679,7 +2689,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2711,10 +2721,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123250520</v>
+        <v>123248138</v>
       </c>
       <c r="B19" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2723,30 +2733,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2761,17 +2771,17 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>588123</v>
+        <v>587888</v>
       </c>
       <c r="R19" t="n">
-        <v>6634219</v>
+        <v>6634183</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2800,7 +2810,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2810,7 +2820,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2842,7 +2852,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123251464</v>
+        <v>123250606</v>
       </c>
       <c r="B20" t="n">
         <v>98365</v>
@@ -2877,7 +2887,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2896,13 +2906,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>588142</v>
+        <v>588109</v>
       </c>
       <c r="R20" t="n">
-        <v>6634249</v>
+        <v>6634191</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2931,7 +2941,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2941,7 +2951,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2973,7 +2983,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123248683</v>
+        <v>123251808</v>
       </c>
       <c r="B21" t="n">
         <v>98365</v>
@@ -3008,12 +3018,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3027,13 +3037,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>587942</v>
+        <v>587915</v>
       </c>
       <c r="R21" t="n">
-        <v>6634200</v>
+        <v>6634215</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3062,7 +3072,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3072,7 +3082,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3104,10 +3114,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123248542</v>
+        <v>123248683</v>
       </c>
       <c r="B22" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3116,46 +3126,55 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kivsta, Kila sn, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>587933</v>
+        <v>587942</v>
       </c>
       <c r="R22" t="n">
-        <v>6634187</v>
+        <v>6634200</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3184,7 +3203,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3194,7 +3213,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3209,26 +3228,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3246,7 +3245,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123249496</v>
+        <v>123250354</v>
       </c>
       <c r="B23" t="n">
         <v>98365</v>
@@ -3281,12 +3280,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3300,13 +3299,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>588070</v>
+        <v>588099</v>
       </c>
       <c r="R23" t="n">
-        <v>6634198</v>
+        <v>6634227</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3335,7 +3334,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3345,7 +3344,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3377,10 +3376,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123250606</v>
+        <v>123248542</v>
       </c>
       <c r="B24" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3389,52 +3388,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Kivsta, Kila sn, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>588109</v>
+        <v>587933</v>
       </c>
       <c r="R24" t="n">
-        <v>6634191</v>
+        <v>6634187</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3466,7 +3456,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3476,7 +3466,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3491,6 +3481,26 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3508,7 +3518,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123250354</v>
+        <v>123249094</v>
       </c>
       <c r="B25" t="n">
         <v>98365</v>
@@ -3543,12 +3553,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3558,17 +3568,17 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>588099</v>
+        <v>587959</v>
       </c>
       <c r="R25" t="n">
-        <v>6634227</v>
+        <v>6634188</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3597,7 +3607,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3607,7 +3617,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3639,7 +3649,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123251549</v>
+        <v>123249452</v>
       </c>
       <c r="B26" t="n">
         <v>98365</v>
@@ -3693,10 +3703,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>588114</v>
+        <v>588053</v>
       </c>
       <c r="R26" t="n">
-        <v>6634233</v>
+        <v>6634200</v>
       </c>
       <c r="S26" t="n">
         <v>7</v>
@@ -3728,7 +3738,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3738,7 +3748,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3770,7 +3780,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123249094</v>
+        <v>123247723</v>
       </c>
       <c r="B27" t="n">
         <v>98365</v>
@@ -3803,34 +3813,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>587959</v>
+        <v>587819</v>
       </c>
       <c r="R27" t="n">
-        <v>6634188</v>
+        <v>6634164</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3859,7 +3855,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3869,7 +3865,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3880,11 +3876,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3901,7 +3892,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123251441</v>
+        <v>123249372</v>
       </c>
       <c r="B28" t="n">
         <v>98365</v>
@@ -3936,7 +3927,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3955,10 +3946,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588163</v>
+        <v>588038</v>
       </c>
       <c r="R28" t="n">
-        <v>6634261</v>
+        <v>6634200</v>
       </c>
       <c r="S28" t="n">
         <v>8</v>
@@ -3990,7 +3981,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4000,7 +3991,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4032,7 +4023,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123249194</v>
+        <v>123250520</v>
       </c>
       <c r="B29" t="n">
         <v>98365</v>
@@ -4067,7 +4058,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4082,14 +4073,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587963</v>
+        <v>588123</v>
       </c>
       <c r="R29" t="n">
-        <v>6634186</v>
+        <v>6634219</v>
       </c>
       <c r="S29" t="n">
         <v>7</v>
@@ -4121,7 +4112,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4131,7 +4122,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4163,10 +4154,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123248138</v>
+        <v>123251549</v>
       </c>
       <c r="B30" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4175,30 +4166,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4213,17 +4204,17 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587888</v>
+        <v>588114</v>
       </c>
       <c r="R30" t="n">
-        <v>6634183</v>
+        <v>6634233</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4252,7 +4243,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4262,7 +4253,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4294,7 +4285,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123247723</v>
+        <v>123251464</v>
       </c>
       <c r="B31" t="n">
         <v>98365</v>
@@ -4327,20 +4318,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>587819</v>
+        <v>588142</v>
       </c>
       <c r="R31" t="n">
-        <v>6634164</v>
+        <v>6634249</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4369,7 +4374,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4379,7 +4384,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4390,6 +4395,11 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4406,10 +4416,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123247980</v>
+        <v>123249194</v>
       </c>
       <c r="B32" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4418,30 +4428,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4460,13 +4470,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>587889</v>
+        <v>587963</v>
       </c>
       <c r="R32" t="n">
-        <v>6634188</v>
+        <v>6634186</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4495,7 +4505,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4505,7 +4515,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4520,16 +4530,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Mark/jord på land</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4678,7 +4678,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123284690</v>
+        <v>123295537</v>
       </c>
       <c r="B34" t="n">
         <v>98365</v>
@@ -4711,16 +4711,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
@@ -4730,13 +4722,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>588177</v>
+        <v>588070</v>
       </c>
       <c r="R34" t="n">
-        <v>6634223</v>
+        <v>6634240</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4908,7 +4900,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123284698</v>
+        <v>123284688</v>
       </c>
       <c r="B36" t="n">
         <v>98365</v>
@@ -4943,12 +4935,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -4960,10 +4952,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>587922</v>
+        <v>588044</v>
       </c>
       <c r="R36" t="n">
-        <v>6634202</v>
+        <v>6634206</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -5023,7 +5015,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123284692</v>
+        <v>123284689</v>
       </c>
       <c r="B37" t="n">
         <v>98365</v>
@@ -5058,7 +5050,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5075,10 +5067,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>588131</v>
+        <v>588176</v>
       </c>
       <c r="R37" t="n">
-        <v>6634212</v>
+        <v>6634236</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5138,7 +5130,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123284696</v>
+        <v>123284690</v>
       </c>
       <c r="B38" t="n">
         <v>98365</v>
@@ -5173,7 +5165,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5190,10 +5182,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>587970</v>
+        <v>588177</v>
       </c>
       <c r="R38" t="n">
-        <v>6634188</v>
+        <v>6634223</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5253,7 +5245,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123284693</v>
+        <v>123284698</v>
       </c>
       <c r="B39" t="n">
         <v>98365</v>
@@ -5288,7 +5280,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5305,10 +5297,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>588083</v>
+        <v>587922</v>
       </c>
       <c r="R39" t="n">
-        <v>6634204</v>
+        <v>6634202</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5368,7 +5360,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123284689</v>
+        <v>123284693</v>
       </c>
       <c r="B40" t="n">
         <v>98365</v>
@@ -5403,7 +5395,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5420,10 +5412,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>588176</v>
+        <v>588083</v>
       </c>
       <c r="R40" t="n">
-        <v>6634236</v>
+        <v>6634204</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5483,7 +5475,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123284694</v>
+        <v>123284696</v>
       </c>
       <c r="B41" t="n">
         <v>98365</v>
@@ -5518,12 +5510,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -5535,10 +5527,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>588076</v>
+        <v>587970</v>
       </c>
       <c r="R41" t="n">
-        <v>6634215</v>
+        <v>6634188</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5598,7 +5590,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123295534</v>
+        <v>123284694</v>
       </c>
       <c r="B42" t="n">
         <v>98365</v>
@@ -5633,12 +5625,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -5650,13 +5642,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>588070</v>
+        <v>588076</v>
       </c>
       <c r="R42" t="n">
-        <v>6634240</v>
+        <v>6634215</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5713,7 +5705,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123284695</v>
+        <v>123284692</v>
       </c>
       <c r="B43" t="n">
         <v>98365</v>
@@ -5748,12 +5740,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -5765,10 +5757,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>588072</v>
+        <v>588131</v>
       </c>
       <c r="R43" t="n">
-        <v>6634226</v>
+        <v>6634212</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5828,7 +5820,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123284688</v>
+        <v>123284695</v>
       </c>
       <c r="B44" t="n">
         <v>98365</v>
@@ -5863,7 +5855,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5880,10 +5872,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>588044</v>
+        <v>588072</v>
       </c>
       <c r="R44" t="n">
-        <v>6634206</v>
+        <v>6634226</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>

--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -3245,10 +3245,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123250354</v>
+        <v>123248542</v>
       </c>
       <c r="B23" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3257,55 +3257,46 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Kivsta, Kila sn, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>588099</v>
+        <v>587933</v>
       </c>
       <c r="R23" t="n">
-        <v>6634227</v>
+        <v>6634187</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3334,7 +3325,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3344,7 +3335,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3359,6 +3350,26 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3376,10 +3387,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123248542</v>
+        <v>123250354</v>
       </c>
       <c r="B24" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3388,46 +3399,55 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kivsta, Kila sn, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587933</v>
+        <v>588099</v>
       </c>
       <c r="R24" t="n">
-        <v>6634187</v>
+        <v>6634227</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3456,7 +3476,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3466,7 +3486,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3481,26 +3501,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>

--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -1794,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123251012</v>
+        <v>123251549</v>
       </c>
       <c r="B12" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,12 +1829,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1848,13 +1848,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588146</v>
+        <v>588114</v>
       </c>
       <c r="R12" t="n">
-        <v>6634204</v>
+        <v>6634233</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1925,10 +1925,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123250437</v>
+        <v>123251389</v>
       </c>
       <c r="B13" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1979,13 +1979,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588103</v>
+        <v>588189</v>
       </c>
       <c r="R13" t="n">
-        <v>6634221</v>
+        <v>6634246</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2056,10 +2056,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123247980</v>
+        <v>123248542</v>
       </c>
       <c r="B14" t="n">
-        <v>105471</v>
+        <v>57497</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2068,55 +2068,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Kivsta, Kila sn, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>587889</v>
+        <v>587933</v>
       </c>
       <c r="R14" t="n">
-        <v>6634188</v>
+        <v>6634187</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2145,7 +2136,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2155,7 +2146,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2172,14 +2163,24 @@
           <t>Skogsmark</t>
         </is>
       </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Mark/jord på land</t>
+          <t>Död trädstam</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Ground/soil on land</t>
+          <t>Dead tree stem # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2197,10 +2198,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123251389</v>
+        <v>123249452</v>
       </c>
       <c r="B15" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2232,12 +2233,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2251,13 +2252,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>588189</v>
+        <v>588053</v>
       </c>
       <c r="R15" t="n">
-        <v>6634246</v>
+        <v>6634200</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2286,7 +2287,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2296,7 +2297,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2328,10 +2329,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123251441</v>
+        <v>123250725</v>
       </c>
       <c r="B16" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2363,7 +2364,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2382,13 +2383,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>588163</v>
+        <v>588146</v>
       </c>
       <c r="R16" t="n">
-        <v>6634261</v>
+        <v>6634204</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2417,7 +2418,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2427,7 +2428,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2459,10 +2460,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123248025</v>
+        <v>123249094</v>
       </c>
       <c r="B17" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2494,12 +2495,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2513,13 +2514,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587890</v>
+        <v>587959</v>
       </c>
       <c r="R17" t="n">
-        <v>6634184</v>
+        <v>6634188</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2548,7 +2549,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2558,7 +2559,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2590,10 +2591,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123249496</v>
+        <v>123248683</v>
       </c>
       <c r="B18" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2625,7 +2626,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2640,17 +2641,17 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>588070</v>
+        <v>587942</v>
       </c>
       <c r="R18" t="n">
-        <v>6634198</v>
+        <v>6634200</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2679,7 +2680,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2689,7 +2690,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2721,10 +2722,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123248138</v>
+        <v>123251464</v>
       </c>
       <c r="B19" t="n">
-        <v>105471</v>
+        <v>98368</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2733,30 +2734,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2771,14 +2772,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587888</v>
+        <v>588142</v>
       </c>
       <c r="R19" t="n">
-        <v>6634183</v>
+        <v>6634249</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -2810,7 +2811,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2820,7 +2821,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2852,10 +2853,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123250606</v>
+        <v>123249372</v>
       </c>
       <c r="B20" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2887,12 +2888,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2906,13 +2907,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>588109</v>
+        <v>588038</v>
       </c>
       <c r="R20" t="n">
-        <v>6634191</v>
+        <v>6634200</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2941,7 +2942,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2951,7 +2952,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2983,10 +2984,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123251808</v>
+        <v>123248138</v>
       </c>
       <c r="B21" t="n">
-        <v>98365</v>
+        <v>105474</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2995,30 +2996,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3037,13 +3038,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>587915</v>
+        <v>587888</v>
       </c>
       <c r="R21" t="n">
-        <v>6634215</v>
+        <v>6634183</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3072,7 +3073,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3082,7 +3083,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3114,10 +3115,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123248683</v>
+        <v>123249496</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3149,7 +3150,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3164,17 +3165,17 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>587942</v>
+        <v>588070</v>
       </c>
       <c r="R22" t="n">
-        <v>6634200</v>
+        <v>6634198</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3203,7 +3204,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3213,7 +3214,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3245,10 +3246,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123248542</v>
+        <v>123248025</v>
       </c>
       <c r="B23" t="n">
-        <v>57494</v>
+        <v>98368</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3257,46 +3258,55 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kivsta, Kila sn, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587933</v>
+        <v>587890</v>
       </c>
       <c r="R23" t="n">
-        <v>6634187</v>
+        <v>6634184</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3325,7 +3335,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3335,7 +3345,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3350,26 +3360,6 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3387,10 +3377,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123250354</v>
+        <v>123249194</v>
       </c>
       <c r="B24" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3422,7 +3412,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3437,17 +3427,17 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>588099</v>
+        <v>587963</v>
       </c>
       <c r="R24" t="n">
-        <v>6634227</v>
+        <v>6634186</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3476,7 +3466,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3486,7 +3476,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3518,10 +3508,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123249094</v>
+        <v>123251808</v>
       </c>
       <c r="B25" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3553,12 +3543,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3572,13 +3562,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587959</v>
+        <v>587915</v>
       </c>
       <c r="R25" t="n">
-        <v>6634188</v>
+        <v>6634215</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3607,7 +3597,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3617,7 +3607,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3649,10 +3639,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123249452</v>
+        <v>123250354</v>
       </c>
       <c r="B26" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3684,7 +3674,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3703,13 +3693,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>588053</v>
+        <v>588099</v>
       </c>
       <c r="R26" t="n">
-        <v>6634200</v>
+        <v>6634227</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3738,7 +3728,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3748,7 +3738,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3780,10 +3770,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123247723</v>
+        <v>123250437</v>
       </c>
       <c r="B27" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3813,20 +3803,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>587819</v>
+        <v>588103</v>
       </c>
       <c r="R27" t="n">
-        <v>6634164</v>
+        <v>6634221</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3855,7 +3859,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3865,7 +3869,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3876,6 +3880,11 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3892,10 +3901,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123249372</v>
+        <v>123247980</v>
       </c>
       <c r="B28" t="n">
-        <v>98365</v>
+        <v>105474</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3904,35 +3913,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3942,14 +3951,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588038</v>
+        <v>587889</v>
       </c>
       <c r="R28" t="n">
-        <v>6634200</v>
+        <v>6634188</v>
       </c>
       <c r="S28" t="n">
         <v>8</v>
@@ -3981,7 +3990,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3991,7 +4000,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4006,6 +4015,16 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4023,10 +4042,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123250520</v>
+        <v>123247723</v>
       </c>
       <c r="B29" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4056,34 +4075,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>588123</v>
+        <v>587819</v>
       </c>
       <c r="R29" t="n">
-        <v>6634219</v>
+        <v>6634164</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4112,7 +4117,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4122,7 +4127,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4133,11 +4138,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4154,10 +4154,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123251549</v>
+        <v>123251441</v>
       </c>
       <c r="B30" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -4208,13 +4208,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>588114</v>
+        <v>588163</v>
       </c>
       <c r="R30" t="n">
-        <v>6634233</v>
+        <v>6634261</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4285,10 +4285,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123251464</v>
+        <v>123250606</v>
       </c>
       <c r="B31" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4339,13 +4339,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>588142</v>
+        <v>588109</v>
       </c>
       <c r="R31" t="n">
-        <v>6634249</v>
+        <v>6634191</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4416,10 +4416,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123249194</v>
+        <v>123250520</v>
       </c>
       <c r="B32" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4466,14 +4466,14 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>587963</v>
+        <v>588123</v>
       </c>
       <c r="R32" t="n">
-        <v>6634186</v>
+        <v>6634219</v>
       </c>
       <c r="S32" t="n">
         <v>7</v>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4550,7 +4550,7 @@
         <v>123251336</v>
       </c>
       <c r="B33" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4678,10 +4678,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123295537</v>
+        <v>123284695</v>
       </c>
       <c r="B34" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4711,8 +4711,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
@@ -4722,13 +4730,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>588070</v>
+        <v>588072</v>
       </c>
       <c r="R34" t="n">
-        <v>6634240</v>
+        <v>6634226</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4785,10 +4793,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123284697</v>
+        <v>123295534</v>
       </c>
       <c r="B35" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4837,13 +4845,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>587914</v>
+        <v>588070</v>
       </c>
       <c r="R35" t="n">
-        <v>6634236</v>
+        <v>6634240</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4900,10 +4908,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123284688</v>
+        <v>123284693</v>
       </c>
       <c r="B36" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4935,12 +4943,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -4952,10 +4960,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>588044</v>
+        <v>588083</v>
       </c>
       <c r="R36" t="n">
-        <v>6634206</v>
+        <v>6634204</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -5015,10 +5023,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123284689</v>
+        <v>123284697</v>
       </c>
       <c r="B37" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5050,7 +5058,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5067,7 +5075,7 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>588176</v>
+        <v>587914</v>
       </c>
       <c r="R37" t="n">
         <v>6634236</v>
@@ -5130,10 +5138,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123284690</v>
+        <v>123284694</v>
       </c>
       <c r="B38" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5165,12 +5173,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -5182,10 +5190,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>588177</v>
+        <v>588076</v>
       </c>
       <c r="R38" t="n">
-        <v>6634223</v>
+        <v>6634215</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5245,10 +5253,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123284698</v>
+        <v>123284689</v>
       </c>
       <c r="B39" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5280,7 +5288,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5297,10 +5305,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>587922</v>
+        <v>588176</v>
       </c>
       <c r="R39" t="n">
-        <v>6634202</v>
+        <v>6634236</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5360,10 +5368,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123284693</v>
+        <v>123284688</v>
       </c>
       <c r="B40" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5395,12 +5403,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -5412,10 +5420,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>588083</v>
+        <v>588044</v>
       </c>
       <c r="R40" t="n">
-        <v>6634204</v>
+        <v>6634206</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5475,10 +5483,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123284696</v>
+        <v>123284692</v>
       </c>
       <c r="B41" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5527,10 +5535,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>587970</v>
+        <v>588131</v>
       </c>
       <c r="R41" t="n">
-        <v>6634188</v>
+        <v>6634212</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5590,10 +5598,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123284694</v>
+        <v>123284698</v>
       </c>
       <c r="B42" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5625,12 +5633,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -5642,10 +5650,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>588076</v>
+        <v>587922</v>
       </c>
       <c r="R42" t="n">
-        <v>6634215</v>
+        <v>6634202</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5705,10 +5713,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123284692</v>
+        <v>123284690</v>
       </c>
       <c r="B43" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5740,7 +5748,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5757,10 +5765,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>588131</v>
+        <v>588177</v>
       </c>
       <c r="R43" t="n">
-        <v>6634212</v>
+        <v>6634223</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5820,10 +5828,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123284695</v>
+        <v>123284696</v>
       </c>
       <c r="B44" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5855,12 +5863,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -5872,10 +5880,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>588072</v>
+        <v>587970</v>
       </c>
       <c r="R44" t="n">
-        <v>6634226</v>
+        <v>6634188</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>

--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -1794,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123251549</v>
+        <v>123247980</v>
       </c>
       <c r="B12" t="n">
-        <v>98368</v>
+        <v>105476</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1806,25 +1806,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1844,17 +1844,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588114</v>
+        <v>587889</v>
       </c>
       <c r="R12" t="n">
-        <v>6634233</v>
+        <v>6634188</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1908,6 +1908,16 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1925,10 +1935,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123251389</v>
+        <v>123251549</v>
       </c>
       <c r="B13" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1960,12 +1970,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1979,13 +1989,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588189</v>
+        <v>588114</v>
       </c>
       <c r="R13" t="n">
-        <v>6634246</v>
+        <v>6634233</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2014,7 +2024,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2024,7 +2034,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2056,10 +2066,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123248542</v>
+        <v>123251012</v>
       </c>
       <c r="B14" t="n">
-        <v>57497</v>
+        <v>98370</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2068,46 +2078,55 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kivsta, Kila sn, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>587933</v>
+        <v>588146</v>
       </c>
       <c r="R14" t="n">
-        <v>6634187</v>
+        <v>6634204</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2136,7 +2155,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2146,7 +2165,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2161,26 +2180,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2198,10 +2197,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123249452</v>
+        <v>123251808</v>
       </c>
       <c r="B15" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2233,7 +2232,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2248,17 +2247,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>588053</v>
+        <v>587915</v>
       </c>
       <c r="R15" t="n">
-        <v>6634200</v>
+        <v>6634215</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2287,7 +2286,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2297,7 +2296,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2329,10 +2328,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123250725</v>
+        <v>123248025</v>
       </c>
       <c r="B16" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2364,12 +2363,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2379,14 +2378,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>588146</v>
+        <v>587890</v>
       </c>
       <c r="R16" t="n">
-        <v>6634204</v>
+        <v>6634184</v>
       </c>
       <c r="S16" t="n">
         <v>6</v>
@@ -2418,7 +2417,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2428,7 +2427,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2460,10 +2459,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123249094</v>
+        <v>123250437</v>
       </c>
       <c r="B17" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2495,7 +2494,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2510,14 +2509,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587959</v>
+        <v>588103</v>
       </c>
       <c r="R17" t="n">
-        <v>6634188</v>
+        <v>6634221</v>
       </c>
       <c r="S17" t="n">
         <v>7</v>
@@ -2549,7 +2548,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2559,7 +2558,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2591,10 +2590,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123248683</v>
+        <v>123249496</v>
       </c>
       <c r="B18" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2626,7 +2625,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2641,17 +2640,17 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587942</v>
+        <v>588070</v>
       </c>
       <c r="R18" t="n">
-        <v>6634200</v>
+        <v>6634198</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2680,7 +2679,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2690,7 +2689,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2722,10 +2721,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123251464</v>
+        <v>123249194</v>
       </c>
       <c r="B19" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2757,7 +2756,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2772,17 +2771,17 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>588142</v>
+        <v>587963</v>
       </c>
       <c r="R19" t="n">
-        <v>6634249</v>
+        <v>6634186</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2811,7 +2810,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2821,7 +2820,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2853,10 +2852,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123249372</v>
+        <v>123251464</v>
       </c>
       <c r="B20" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2888,12 +2887,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2907,10 +2906,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>588038</v>
+        <v>588142</v>
       </c>
       <c r="R20" t="n">
-        <v>6634200</v>
+        <v>6634249</v>
       </c>
       <c r="S20" t="n">
         <v>8</v>
@@ -2942,7 +2941,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2952,7 +2951,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2987,7 +2986,7 @@
         <v>123248138</v>
       </c>
       <c r="B21" t="n">
-        <v>105474</v>
+        <v>105476</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3115,10 +3114,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123249496</v>
+        <v>123247723</v>
       </c>
       <c r="B22" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3148,34 +3147,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>588070</v>
+        <v>587819</v>
       </c>
       <c r="R22" t="n">
-        <v>6634198</v>
+        <v>6634164</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3204,7 +3189,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3214,7 +3199,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3225,11 +3210,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3246,10 +3226,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123248025</v>
+        <v>123248683</v>
       </c>
       <c r="B23" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3281,12 +3261,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3300,13 +3280,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587890</v>
+        <v>587942</v>
       </c>
       <c r="R23" t="n">
-        <v>6634184</v>
+        <v>6634200</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3335,7 +3315,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3345,7 +3325,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3377,10 +3357,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123249194</v>
+        <v>123251389</v>
       </c>
       <c r="B24" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3412,12 +3392,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3427,17 +3407,17 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587963</v>
+        <v>588189</v>
       </c>
       <c r="R24" t="n">
-        <v>6634186</v>
+        <v>6634246</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3466,7 +3446,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3476,7 +3456,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3508,10 +3488,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123251808</v>
+        <v>123250354</v>
       </c>
       <c r="B25" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3558,17 +3538,17 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587915</v>
+        <v>588099</v>
       </c>
       <c r="R25" t="n">
-        <v>6634215</v>
+        <v>6634227</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3597,7 +3577,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3607,7 +3587,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3639,10 +3619,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123250354</v>
+        <v>123249452</v>
       </c>
       <c r="B26" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3674,7 +3654,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3693,13 +3673,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>588099</v>
+        <v>588053</v>
       </c>
       <c r="R26" t="n">
-        <v>6634227</v>
+        <v>6634200</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3728,7 +3708,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3738,7 +3718,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3770,10 +3750,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123250437</v>
+        <v>123249094</v>
       </c>
       <c r="B27" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3805,7 +3785,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3820,14 +3800,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>588103</v>
+        <v>587959</v>
       </c>
       <c r="R27" t="n">
-        <v>6634221</v>
+        <v>6634188</v>
       </c>
       <c r="S27" t="n">
         <v>7</v>
@@ -3859,7 +3839,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3869,7 +3849,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3901,10 +3881,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123247980</v>
+        <v>123250606</v>
       </c>
       <c r="B28" t="n">
-        <v>105474</v>
+        <v>98370</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3913,30 +3893,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3951,17 +3931,17 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>587889</v>
+        <v>588109</v>
       </c>
       <c r="R28" t="n">
-        <v>6634188</v>
+        <v>6634191</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3990,7 +3970,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4000,7 +3980,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4015,16 +3995,6 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Mark/jord på land</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4042,10 +4012,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123247723</v>
+        <v>123248542</v>
       </c>
       <c r="B29" t="n">
-        <v>98368</v>
+        <v>57497</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4054,41 +4024,46 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Kivsta, Kila sn, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587819</v>
+        <v>587933</v>
       </c>
       <c r="R29" t="n">
-        <v>6634164</v>
+        <v>6634187</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4117,7 +4092,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4127,7 +4102,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4138,6 +4113,31 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4157,7 +4157,7 @@
         <v>123251441</v>
       </c>
       <c r="B30" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4285,10 +4285,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123250606</v>
+        <v>123250520</v>
       </c>
       <c r="B31" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4339,13 +4339,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>588109</v>
+        <v>588123</v>
       </c>
       <c r="R31" t="n">
-        <v>6634191</v>
+        <v>6634219</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4416,10 +4416,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123250520</v>
+        <v>123249372</v>
       </c>
       <c r="B32" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4451,12 +4451,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4470,13 +4470,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>588123</v>
+        <v>588038</v>
       </c>
       <c r="R32" t="n">
-        <v>6634219</v>
+        <v>6634200</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4550,7 +4550,7 @@
         <v>123251336</v>
       </c>
       <c r="B33" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4678,10 +4678,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123284695</v>
+        <v>123284690</v>
       </c>
       <c r="B34" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>588072</v>
+        <v>588177</v>
       </c>
       <c r="R34" t="n">
-        <v>6634226</v>
+        <v>6634223</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4793,10 +4793,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123295534</v>
+        <v>123284697</v>
       </c>
       <c r="B35" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>588070</v>
+        <v>587914</v>
       </c>
       <c r="R35" t="n">
-        <v>6634240</v>
+        <v>6634236</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>123284693</v>
       </c>
       <c r="B36" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5023,10 +5023,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123284697</v>
+        <v>123284694</v>
       </c>
       <c r="B37" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5058,12 +5058,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>587914</v>
+        <v>588076</v>
       </c>
       <c r="R37" t="n">
-        <v>6634236</v>
+        <v>6634215</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5138,10 +5138,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123284694</v>
+        <v>123295537</v>
       </c>
       <c r="B38" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5171,16 +5171,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -5190,13 +5182,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>588076</v>
+        <v>588070</v>
       </c>
       <c r="R38" t="n">
-        <v>6634215</v>
+        <v>6634240</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5253,10 +5245,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123284689</v>
+        <v>123284688</v>
       </c>
       <c r="B39" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5288,12 +5280,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -5305,10 +5297,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>588176</v>
+        <v>588044</v>
       </c>
       <c r="R39" t="n">
-        <v>6634236</v>
+        <v>6634206</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5368,10 +5360,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123284688</v>
+        <v>123284695</v>
       </c>
       <c r="B40" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5403,7 +5395,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5420,10 +5412,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>588044</v>
+        <v>588072</v>
       </c>
       <c r="R40" t="n">
-        <v>6634206</v>
+        <v>6634226</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5483,10 +5475,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123284692</v>
+        <v>123284689</v>
       </c>
       <c r="B41" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5518,7 +5510,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5535,10 +5527,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>588131</v>
+        <v>588176</v>
       </c>
       <c r="R41" t="n">
-        <v>6634212</v>
+        <v>6634236</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5601,7 +5593,7 @@
         <v>123284698</v>
       </c>
       <c r="B42" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5713,10 +5705,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123284690</v>
+        <v>123284696</v>
       </c>
       <c r="B43" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5748,7 +5740,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5765,10 +5757,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>588177</v>
+        <v>587970</v>
       </c>
       <c r="R43" t="n">
-        <v>6634223</v>
+        <v>6634188</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5828,10 +5820,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123284696</v>
+        <v>123284692</v>
       </c>
       <c r="B44" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5880,10 +5872,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>587970</v>
+        <v>588131</v>
       </c>
       <c r="R44" t="n">
-        <v>6634188</v>
+        <v>6634212</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>

--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -2328,7 +2328,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123248025</v>
+        <v>123250437</v>
       </c>
       <c r="B16" t="n">
         <v>98370</v>
@@ -2363,12 +2363,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2378,17 +2378,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587890</v>
+        <v>588103</v>
       </c>
       <c r="R16" t="n">
-        <v>6634184</v>
+        <v>6634221</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2459,7 +2459,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123250437</v>
+        <v>123248025</v>
       </c>
       <c r="B17" t="n">
         <v>98370</v>
@@ -2494,12 +2494,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2509,17 +2509,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>588103</v>
+        <v>587890</v>
       </c>
       <c r="R17" t="n">
-        <v>6634221</v>
+        <v>6634184</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -4285,7 +4285,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123250520</v>
+        <v>123249372</v>
       </c>
       <c r="B31" t="n">
         <v>98370</v>
@@ -4320,12 +4320,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4339,13 +4339,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>588123</v>
+        <v>588038</v>
       </c>
       <c r="R31" t="n">
-        <v>6634219</v>
+        <v>6634200</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4416,7 +4416,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123249372</v>
+        <v>123250520</v>
       </c>
       <c r="B32" t="n">
         <v>98370</v>
@@ -4451,12 +4451,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4470,13 +4470,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>588038</v>
+        <v>588123</v>
       </c>
       <c r="R32" t="n">
-        <v>6634200</v>
+        <v>6634219</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -1794,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123247980</v>
+        <v>123251389</v>
       </c>
       <c r="B12" t="n">
-        <v>105476</v>
+        <v>98376</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1806,35 +1806,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1844,17 +1844,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587889</v>
+        <v>588189</v>
       </c>
       <c r="R12" t="n">
-        <v>6634188</v>
+        <v>6634246</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1908,16 +1908,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Mark/jord på land</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1935,10 +1925,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123251549</v>
+        <v>123248683</v>
       </c>
       <c r="B13" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1970,12 +1960,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1985,17 +1975,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588114</v>
+        <v>587942</v>
       </c>
       <c r="R13" t="n">
-        <v>6634233</v>
+        <v>6634200</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2024,7 +2014,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2034,7 +2024,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2066,10 +2056,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123251012</v>
+        <v>123247723</v>
       </c>
       <c r="B14" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2099,31 +2089,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588146</v>
+        <v>587819</v>
       </c>
       <c r="R14" t="n">
-        <v>6634204</v>
+        <v>6634164</v>
       </c>
       <c r="S14" t="n">
         <v>6</v>
@@ -2155,7 +2131,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2165,7 +2141,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2176,11 +2152,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2197,10 +2168,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123251808</v>
+        <v>123248542</v>
       </c>
       <c r="B15" t="n">
-        <v>98370</v>
+        <v>57497</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2209,52 +2180,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Kivsta, Kila sn, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>587915</v>
+        <v>587933</v>
       </c>
       <c r="R15" t="n">
-        <v>6634215</v>
+        <v>6634187</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2286,7 +2248,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2296,7 +2258,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2311,6 +2273,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2328,10 +2310,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123250437</v>
+        <v>123250725</v>
       </c>
       <c r="B16" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2363,7 +2345,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2382,13 +2364,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>588103</v>
+        <v>588146</v>
       </c>
       <c r="R16" t="n">
-        <v>6634221</v>
+        <v>6634204</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2417,7 +2399,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2427,7 +2409,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2459,10 +2441,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123248025</v>
+        <v>123250606</v>
       </c>
       <c r="B17" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2494,7 +2476,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2509,17 +2491,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587890</v>
+        <v>588109</v>
       </c>
       <c r="R17" t="n">
-        <v>6634184</v>
+        <v>6634191</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2548,7 +2530,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2558,7 +2540,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2593,7 +2575,7 @@
         <v>123249496</v>
       </c>
       <c r="B18" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2721,10 +2703,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123249194</v>
+        <v>123251441</v>
       </c>
       <c r="B19" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2756,12 +2738,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2771,17 +2753,17 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587963</v>
+        <v>588163</v>
       </c>
       <c r="R19" t="n">
-        <v>6634186</v>
+        <v>6634261</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2810,7 +2792,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2820,7 +2802,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2852,10 +2834,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123251464</v>
+        <v>123248025</v>
       </c>
       <c r="B20" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2887,7 +2869,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2902,17 +2884,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>588142</v>
+        <v>587890</v>
       </c>
       <c r="R20" t="n">
-        <v>6634249</v>
+        <v>6634184</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2941,7 +2923,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2951,7 +2933,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2983,10 +2965,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123248138</v>
+        <v>123249372</v>
       </c>
       <c r="B21" t="n">
-        <v>105476</v>
+        <v>98376</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2995,35 +2977,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3033,14 +3015,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>587888</v>
+        <v>588038</v>
       </c>
       <c r="R21" t="n">
-        <v>6634183</v>
+        <v>6634200</v>
       </c>
       <c r="S21" t="n">
         <v>8</v>
@@ -3072,7 +3054,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3082,7 +3064,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3114,10 +3096,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123247723</v>
+        <v>123249094</v>
       </c>
       <c r="B22" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3147,20 +3129,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>587819</v>
+        <v>587959</v>
       </c>
       <c r="R22" t="n">
-        <v>6634164</v>
+        <v>6634188</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3189,7 +3185,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3199,7 +3195,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3210,6 +3206,11 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3226,10 +3227,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123248683</v>
+        <v>123250437</v>
       </c>
       <c r="B23" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3261,7 +3262,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3276,17 +3277,17 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587942</v>
+        <v>588103</v>
       </c>
       <c r="R23" t="n">
-        <v>6634200</v>
+        <v>6634221</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3315,7 +3316,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3325,7 +3326,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3357,10 +3358,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123251389</v>
+        <v>123250520</v>
       </c>
       <c r="B24" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3392,12 +3393,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3411,13 +3412,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>588189</v>
+        <v>588123</v>
       </c>
       <c r="R24" t="n">
-        <v>6634246</v>
+        <v>6634219</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3446,7 +3447,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3456,7 +3457,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3488,10 +3489,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123250354</v>
+        <v>123251808</v>
       </c>
       <c r="B25" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3538,17 +3539,17 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>588099</v>
+        <v>587915</v>
       </c>
       <c r="R25" t="n">
-        <v>6634227</v>
+        <v>6634215</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3577,7 +3578,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3587,7 +3588,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3619,10 +3620,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123249452</v>
+        <v>123249194</v>
       </c>
       <c r="B26" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3654,7 +3655,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3669,14 +3670,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>588053</v>
+        <v>587963</v>
       </c>
       <c r="R26" t="n">
-        <v>6634200</v>
+        <v>6634186</v>
       </c>
       <c r="S26" t="n">
         <v>7</v>
@@ -3708,7 +3709,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3718,7 +3719,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3750,10 +3751,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123249094</v>
+        <v>123250354</v>
       </c>
       <c r="B27" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3785,12 +3786,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3800,17 +3801,17 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>587959</v>
+        <v>588099</v>
       </c>
       <c r="R27" t="n">
-        <v>6634188</v>
+        <v>6634227</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3839,7 +3840,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3849,7 +3850,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3881,10 +3882,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123250606</v>
+        <v>123248138</v>
       </c>
       <c r="B28" t="n">
-        <v>98370</v>
+        <v>105482</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3893,30 +3894,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3931,17 +3932,17 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588109</v>
+        <v>587888</v>
       </c>
       <c r="R28" t="n">
-        <v>6634191</v>
+        <v>6634183</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3970,7 +3971,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3980,7 +3981,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4012,10 +4013,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123248542</v>
+        <v>123251549</v>
       </c>
       <c r="B29" t="n">
-        <v>57497</v>
+        <v>98376</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4024,46 +4025,55 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kivsta, Kila sn, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587933</v>
+        <v>588114</v>
       </c>
       <c r="R29" t="n">
-        <v>6634187</v>
+        <v>6634233</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4092,7 +4102,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4102,7 +4112,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4117,26 +4127,6 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4154,10 +4144,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123251441</v>
+        <v>123249452</v>
       </c>
       <c r="B30" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4189,12 +4179,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -4208,13 +4198,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>588163</v>
+        <v>588053</v>
       </c>
       <c r="R30" t="n">
-        <v>6634261</v>
+        <v>6634200</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4243,7 +4233,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4253,7 +4243,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4285,10 +4275,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123249372</v>
+        <v>123251464</v>
       </c>
       <c r="B31" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4320,12 +4310,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4339,10 +4329,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>588038</v>
+        <v>588142</v>
       </c>
       <c r="R31" t="n">
-        <v>6634200</v>
+        <v>6634249</v>
       </c>
       <c r="S31" t="n">
         <v>8</v>
@@ -4374,7 +4364,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4384,7 +4374,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4416,10 +4406,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123250520</v>
+        <v>123247980</v>
       </c>
       <c r="B32" t="n">
-        <v>98370</v>
+        <v>105482</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4428,30 +4418,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4466,17 +4456,17 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>588123</v>
+        <v>587889</v>
       </c>
       <c r="R32" t="n">
-        <v>6634219</v>
+        <v>6634188</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4505,7 +4495,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4515,7 +4505,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4530,6 +4520,16 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4550,7 +4550,7 @@
         <v>123251336</v>
       </c>
       <c r="B33" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4678,10 +4678,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123284690</v>
+        <v>123284688</v>
       </c>
       <c r="B34" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>588177</v>
+        <v>588044</v>
       </c>
       <c r="R34" t="n">
-        <v>6634223</v>
+        <v>6634206</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4793,10 +4793,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123284697</v>
+        <v>123284698</v>
       </c>
       <c r="B35" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>587914</v>
+        <v>587922</v>
       </c>
       <c r="R35" t="n">
-        <v>6634236</v>
+        <v>6634202</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4908,10 +4908,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123284693</v>
+        <v>123284692</v>
       </c>
       <c r="B36" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4960,10 +4960,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>588083</v>
+        <v>588131</v>
       </c>
       <c r="R36" t="n">
-        <v>6634204</v>
+        <v>6634212</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -5023,10 +5023,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123284694</v>
+        <v>123295534</v>
       </c>
       <c r="B37" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5058,12 +5058,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -5075,13 +5075,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>588076</v>
+        <v>588070</v>
       </c>
       <c r="R37" t="n">
-        <v>6634215</v>
+        <v>6634240</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5138,10 +5138,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123295537</v>
+        <v>123284693</v>
       </c>
       <c r="B38" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5171,8 +5171,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -5182,13 +5190,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>588070</v>
+        <v>588083</v>
       </c>
       <c r="R38" t="n">
-        <v>6634240</v>
+        <v>6634204</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5245,10 +5253,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123284688</v>
+        <v>123284696</v>
       </c>
       <c r="B39" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5280,12 +5288,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -5297,10 +5305,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>588044</v>
+        <v>587970</v>
       </c>
       <c r="R39" t="n">
-        <v>6634206</v>
+        <v>6634188</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5360,10 +5368,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123284695</v>
+        <v>123284689</v>
       </c>
       <c r="B40" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5395,12 +5403,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -5412,10 +5420,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>588072</v>
+        <v>588176</v>
       </c>
       <c r="R40" t="n">
-        <v>6634226</v>
+        <v>6634236</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5475,10 +5483,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123284689</v>
+        <v>123284694</v>
       </c>
       <c r="B41" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5510,12 +5518,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -5527,10 +5535,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>588176</v>
+        <v>588076</v>
       </c>
       <c r="R41" t="n">
-        <v>6634236</v>
+        <v>6634215</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5590,10 +5598,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123284698</v>
+        <v>123284695</v>
       </c>
       <c r="B42" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5625,12 +5633,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -5642,10 +5650,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>587922</v>
+        <v>588072</v>
       </c>
       <c r="R42" t="n">
-        <v>6634202</v>
+        <v>6634226</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5705,10 +5713,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123284696</v>
+        <v>123284697</v>
       </c>
       <c r="B43" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5740,7 +5748,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5757,10 +5765,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>587970</v>
+        <v>587914</v>
       </c>
       <c r="R43" t="n">
-        <v>6634188</v>
+        <v>6634236</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5820,10 +5828,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123284692</v>
+        <v>123284690</v>
       </c>
       <c r="B44" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5855,7 +5863,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5872,10 +5880,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>588131</v>
+        <v>588177</v>
       </c>
       <c r="R44" t="n">
-        <v>6634212</v>
+        <v>6634223</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>

--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -3497,7 +3497,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123250354</v>
+        <v>123248025</v>
       </c>
       <c r="B25" t="n">
         <v>98379</v>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3547,17 +3547,17 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>588099</v>
+        <v>587890</v>
       </c>
       <c r="R25" t="n">
-        <v>6634227</v>
+        <v>6634184</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3628,7 +3628,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123248025</v>
+        <v>123250354</v>
       </c>
       <c r="B26" t="n">
         <v>98379</v>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3678,17 +3678,17 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587890</v>
+        <v>588099</v>
       </c>
       <c r="R26" t="n">
-        <v>6634184</v>
+        <v>6634227</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -1794,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123251012</v>
+        <v>123251464</v>
       </c>
       <c r="B12" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,12 +1829,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1848,13 +1848,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588146</v>
+        <v>588142</v>
       </c>
       <c r="R12" t="n">
-        <v>6634204</v>
+        <v>6634249</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1925,10 +1925,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123251389</v>
+        <v>123250520</v>
       </c>
       <c r="B13" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1960,12 +1960,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1979,13 +1979,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588189</v>
+        <v>588123</v>
       </c>
       <c r="R13" t="n">
-        <v>6634246</v>
+        <v>6634219</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2056,10 +2056,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123251464</v>
+        <v>123251549</v>
       </c>
       <c r="B14" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2110,13 +2110,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588142</v>
+        <v>588114</v>
       </c>
       <c r="R14" t="n">
-        <v>6634249</v>
+        <v>6634233</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2187,10 +2187,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123250606</v>
+        <v>123251389</v>
       </c>
       <c r="B15" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2222,12 +2222,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2241,13 +2241,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>588109</v>
+        <v>588189</v>
       </c>
       <c r="R15" t="n">
-        <v>6634191</v>
+        <v>6634246</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2318,10 +2318,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123249372</v>
+        <v>123250437</v>
       </c>
       <c r="B16" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2372,13 +2372,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>588038</v>
+        <v>588103</v>
       </c>
       <c r="R16" t="n">
-        <v>6634200</v>
+        <v>6634221</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2449,10 +2449,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123249496</v>
+        <v>123249194</v>
       </c>
       <c r="B17" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2484,12 +2484,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2499,17 +2499,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>588070</v>
+        <v>587963</v>
       </c>
       <c r="R17" t="n">
-        <v>6634198</v>
+        <v>6634186</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2580,10 +2580,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123249452</v>
+        <v>123249094</v>
       </c>
       <c r="B18" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2615,12 +2615,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2630,14 +2630,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>588053</v>
+        <v>587959</v>
       </c>
       <c r="R18" t="n">
-        <v>6634200</v>
+        <v>6634188</v>
       </c>
       <c r="S18" t="n">
         <v>7</v>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2711,10 +2711,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123248683</v>
+        <v>123250354</v>
       </c>
       <c r="B19" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2746,12 +2746,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2761,14 +2761,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587942</v>
+        <v>588099</v>
       </c>
       <c r="R19" t="n">
-        <v>6634200</v>
+        <v>6634227</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2842,10 +2842,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123251808</v>
+        <v>123247723</v>
       </c>
       <c r="B20" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2875,34 +2875,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>587915</v>
+        <v>587819</v>
       </c>
       <c r="R20" t="n">
-        <v>6634215</v>
+        <v>6634164</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2931,7 +2917,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2941,7 +2927,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2952,11 +2938,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2976,7 +2957,7 @@
         <v>123251441</v>
       </c>
       <c r="B21" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3104,10 +3085,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123251549</v>
+        <v>123249496</v>
       </c>
       <c r="B22" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3139,12 +3120,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3158,13 +3139,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>588114</v>
+        <v>588070</v>
       </c>
       <c r="R22" t="n">
-        <v>6634233</v>
+        <v>6634198</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3193,7 +3174,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3203,7 +3184,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3235,10 +3216,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123250437</v>
+        <v>123249372</v>
       </c>
       <c r="B23" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3270,7 +3251,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3289,13 +3270,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>588103</v>
+        <v>588038</v>
       </c>
       <c r="R23" t="n">
-        <v>6634221</v>
+        <v>6634200</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3324,7 +3305,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3334,7 +3315,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3366,10 +3347,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123250520</v>
+        <v>123247980</v>
       </c>
       <c r="B24" t="n">
-        <v>98379</v>
+        <v>105502</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3378,30 +3359,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3416,17 +3397,17 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>588123</v>
+        <v>587889</v>
       </c>
       <c r="R24" t="n">
-        <v>6634219</v>
+        <v>6634188</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3455,7 +3436,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3465,7 +3446,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3480,6 +3461,16 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3497,10 +3488,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123248025</v>
+        <v>123251808</v>
       </c>
       <c r="B25" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3532,7 +3523,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3551,13 +3542,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587890</v>
+        <v>587915</v>
       </c>
       <c r="R25" t="n">
-        <v>6634184</v>
+        <v>6634215</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3586,7 +3577,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3596,7 +3587,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3628,10 +3619,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123250354</v>
+        <v>123248025</v>
       </c>
       <c r="B26" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3663,7 +3654,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3678,17 +3669,17 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>588099</v>
+        <v>587890</v>
       </c>
       <c r="R26" t="n">
-        <v>6634227</v>
+        <v>6634184</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3717,7 +3708,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3727,7 +3718,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3759,10 +3750,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123249094</v>
+        <v>123251012</v>
       </c>
       <c r="B27" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3794,7 +3785,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3809,17 +3800,17 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>587959</v>
+        <v>588146</v>
       </c>
       <c r="R27" t="n">
-        <v>6634188</v>
+        <v>6634204</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3848,7 +3839,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3858,7 +3849,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3890,10 +3881,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123247723</v>
+        <v>123248542</v>
       </c>
       <c r="B28" t="n">
-        <v>98379</v>
+        <v>57503</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3902,41 +3893,46 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Kivsta, Kila sn, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>587819</v>
+        <v>587933</v>
       </c>
       <c r="R28" t="n">
-        <v>6634164</v>
+        <v>6634187</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3965,7 +3961,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3975,7 +3971,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3986,6 +3982,31 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -4002,10 +4023,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123248542</v>
+        <v>123248683</v>
       </c>
       <c r="B29" t="n">
-        <v>57497</v>
+        <v>98396</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4014,46 +4035,55 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kivsta, Kila sn, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587933</v>
+        <v>587942</v>
       </c>
       <c r="R29" t="n">
-        <v>6634187</v>
+        <v>6634200</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4082,7 +4112,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4092,7 +4122,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4107,26 +4137,6 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4144,10 +4154,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123247980</v>
+        <v>123249452</v>
       </c>
       <c r="B30" t="n">
-        <v>105485</v>
+        <v>98396</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4156,25 +4166,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4194,17 +4204,17 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587889</v>
+        <v>588053</v>
       </c>
       <c r="R30" t="n">
-        <v>6634188</v>
+        <v>6634200</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4233,7 +4243,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4243,7 +4253,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4258,16 +4268,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Mark/jord på land</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4285,10 +4285,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123248138</v>
+        <v>123250606</v>
       </c>
       <c r="B31" t="n">
-        <v>105485</v>
+        <v>98396</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4297,30 +4297,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4335,17 +4335,17 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>587888</v>
+        <v>588109</v>
       </c>
       <c r="R31" t="n">
-        <v>6634183</v>
+        <v>6634191</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4416,10 +4416,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123249194</v>
+        <v>123248138</v>
       </c>
       <c r="B32" t="n">
-        <v>98379</v>
+        <v>105502</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4428,30 +4428,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4470,13 +4470,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>587963</v>
+        <v>587888</v>
       </c>
       <c r="R32" t="n">
-        <v>6634186</v>
+        <v>6634183</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4550,7 +4550,7 @@
         <v>123251336</v>
       </c>
       <c r="B33" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4678,10 +4678,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123284693</v>
+        <v>123284690</v>
       </c>
       <c r="B34" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>588083</v>
+        <v>588177</v>
       </c>
       <c r="R34" t="n">
-        <v>6634204</v>
+        <v>6634223</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4793,10 +4793,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123295537</v>
+        <v>123284693</v>
       </c>
       <c r="B35" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4826,8 +4826,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4837,13 +4845,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>588070</v>
+        <v>588083</v>
       </c>
       <c r="R35" t="n">
-        <v>6634240</v>
+        <v>6634204</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4900,10 +4908,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123284697</v>
+        <v>123295537</v>
       </c>
       <c r="B36" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4933,16 +4941,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
@@ -4952,13 +4952,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>587914</v>
+        <v>588070</v>
       </c>
       <c r="R36" t="n">
-        <v>6634236</v>
+        <v>6634240</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>123284689</v>
       </c>
       <c r="B37" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5130,10 +5130,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123284688</v>
+        <v>123284694</v>
       </c>
       <c r="B38" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5182,10 +5182,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>588044</v>
+        <v>588076</v>
       </c>
       <c r="R38" t="n">
-        <v>6634206</v>
+        <v>6634215</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5245,10 +5245,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123284692</v>
+        <v>123284688</v>
       </c>
       <c r="B39" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5280,12 +5280,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -5297,10 +5297,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>588131</v>
+        <v>588044</v>
       </c>
       <c r="R39" t="n">
-        <v>6634212</v>
+        <v>6634206</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5360,10 +5360,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123284698</v>
+        <v>123284692</v>
       </c>
       <c r="B40" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5412,10 +5412,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>587922</v>
+        <v>588131</v>
       </c>
       <c r="R40" t="n">
-        <v>6634202</v>
+        <v>6634212</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5475,10 +5475,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123284694</v>
+        <v>123284696</v>
       </c>
       <c r="B41" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -5527,10 +5527,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>588076</v>
+        <v>587970</v>
       </c>
       <c r="R41" t="n">
-        <v>6634215</v>
+        <v>6634188</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5590,10 +5590,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123284696</v>
+        <v>123284695</v>
       </c>
       <c r="B42" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5625,12 +5625,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -5642,10 +5642,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>587970</v>
+        <v>588072</v>
       </c>
       <c r="R42" t="n">
-        <v>6634188</v>
+        <v>6634226</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5705,10 +5705,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123284690</v>
+        <v>123284698</v>
       </c>
       <c r="B43" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5757,10 +5757,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>588177</v>
+        <v>587922</v>
       </c>
       <c r="R43" t="n">
-        <v>6634223</v>
+        <v>6634202</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5820,10 +5820,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123284695</v>
+        <v>123284697</v>
       </c>
       <c r="B44" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5855,12 +5855,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>588072</v>
+        <v>587914</v>
       </c>
       <c r="R44" t="n">
-        <v>6634226</v>
+        <v>6634236</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>

--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -3881,10 +3881,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123248542</v>
+        <v>123248683</v>
       </c>
       <c r="B28" t="n">
-        <v>57503</v>
+        <v>98396</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3893,46 +3893,55 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kivsta, Kila sn, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>587933</v>
+        <v>587942</v>
       </c>
       <c r="R28" t="n">
-        <v>6634187</v>
+        <v>6634200</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3961,7 +3970,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3971,7 +3980,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3986,26 +3995,6 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4023,7 +4012,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123248683</v>
+        <v>123249452</v>
       </c>
       <c r="B29" t="n">
         <v>98396</v>
@@ -4058,12 +4047,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -4073,17 +4062,17 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587942</v>
+        <v>588053</v>
       </c>
       <c r="R29" t="n">
         <v>6634200</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4112,7 +4101,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4122,7 +4111,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4154,10 +4143,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123249452</v>
+        <v>123248542</v>
       </c>
       <c r="B30" t="n">
-        <v>98396</v>
+        <v>57503</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4166,55 +4155,46 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Kivsta, Kila sn, Vstm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>588053</v>
+        <v>587933</v>
       </c>
       <c r="R30" t="n">
-        <v>6634200</v>
+        <v>6634187</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4243,7 +4223,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4253,7 +4233,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4268,6 +4248,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>

--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -3619,7 +3619,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123248025</v>
+        <v>123251012</v>
       </c>
       <c r="B26" t="n">
         <v>98396</v>
@@ -3654,12 +3654,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3669,14 +3669,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587890</v>
+        <v>588146</v>
       </c>
       <c r="R26" t="n">
-        <v>6634184</v>
+        <v>6634204</v>
       </c>
       <c r="S26" t="n">
         <v>6</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3750,7 +3750,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123251012</v>
+        <v>123248025</v>
       </c>
       <c r="B27" t="n">
         <v>98396</v>
@@ -3785,12 +3785,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3800,14 +3800,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>588146</v>
+        <v>587890</v>
       </c>
       <c r="R27" t="n">
-        <v>6634204</v>
+        <v>6634184</v>
       </c>
       <c r="S27" t="n">
         <v>6</v>
@@ -3839,7 +3839,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3881,10 +3881,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123248683</v>
+        <v>123248542</v>
       </c>
       <c r="B28" t="n">
-        <v>98396</v>
+        <v>57503</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3893,55 +3893,46 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Kivsta, Kila sn, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>587942</v>
+        <v>587933</v>
       </c>
       <c r="R28" t="n">
-        <v>6634200</v>
+        <v>6634187</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3970,7 +3961,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3980,7 +3971,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3995,6 +3986,26 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4012,7 +4023,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123249452</v>
+        <v>123248683</v>
       </c>
       <c r="B29" t="n">
         <v>98396</v>
@@ -4047,12 +4058,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -4062,17 +4073,17 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>588053</v>
+        <v>587942</v>
       </c>
       <c r="R29" t="n">
         <v>6634200</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4101,7 +4112,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4111,7 +4122,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4143,10 +4154,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123248542</v>
+        <v>123249452</v>
       </c>
       <c r="B30" t="n">
-        <v>57503</v>
+        <v>98396</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4155,46 +4166,55 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kivsta, Kila sn, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587933</v>
+        <v>588053</v>
       </c>
       <c r="R30" t="n">
-        <v>6634187</v>
+        <v>6634200</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4223,7 +4243,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4233,7 +4253,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4248,26 +4268,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>

--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -1794,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123251464</v>
+        <v>123249496</v>
       </c>
       <c r="B12" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,12 +1829,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1848,13 +1848,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588142</v>
+        <v>588070</v>
       </c>
       <c r="R12" t="n">
-        <v>6634249</v>
+        <v>6634198</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1925,10 +1925,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123250520</v>
+        <v>123249452</v>
       </c>
       <c r="B13" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588123</v>
+        <v>588053</v>
       </c>
       <c r="R13" t="n">
-        <v>6634219</v>
+        <v>6634200</v>
       </c>
       <c r="S13" t="n">
         <v>7</v>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2056,10 +2056,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123251549</v>
+        <v>123249094</v>
       </c>
       <c r="B14" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2091,12 +2091,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2106,14 +2106,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588114</v>
+        <v>587959</v>
       </c>
       <c r="R14" t="n">
-        <v>6634233</v>
+        <v>6634188</v>
       </c>
       <c r="S14" t="n">
         <v>7</v>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2187,10 +2187,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123251389</v>
+        <v>123250725</v>
       </c>
       <c r="B15" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2241,10 +2241,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>588189</v>
+        <v>588146</v>
       </c>
       <c r="R15" t="n">
-        <v>6634246</v>
+        <v>6634204</v>
       </c>
       <c r="S15" t="n">
         <v>6</v>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2318,10 +2318,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123250437</v>
+        <v>123249372</v>
       </c>
       <c r="B16" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2372,13 +2372,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>588103</v>
+        <v>588038</v>
       </c>
       <c r="R16" t="n">
-        <v>6634221</v>
+        <v>6634200</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2449,10 +2449,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123249194</v>
+        <v>123247723</v>
       </c>
       <c r="B17" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2482,34 +2482,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587963</v>
+        <v>587819</v>
       </c>
       <c r="R17" t="n">
-        <v>6634186</v>
+        <v>6634164</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2538,7 +2524,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2548,7 +2534,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2559,11 +2545,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2580,10 +2561,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123249094</v>
+        <v>123251808</v>
       </c>
       <c r="B18" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2615,12 +2596,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2634,13 +2615,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587959</v>
+        <v>587915</v>
       </c>
       <c r="R18" t="n">
-        <v>6634188</v>
+        <v>6634215</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2669,7 +2650,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2679,7 +2660,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2711,10 +2692,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123250354</v>
+        <v>123251389</v>
       </c>
       <c r="B19" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2746,12 +2727,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2765,13 +2746,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>588099</v>
+        <v>588189</v>
       </c>
       <c r="R19" t="n">
-        <v>6634227</v>
+        <v>6634246</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2800,7 +2781,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2810,7 +2791,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2842,10 +2823,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123247723</v>
+        <v>123248138</v>
       </c>
       <c r="B20" t="n">
-        <v>98396</v>
+        <v>105518</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2854,41 +2835,55 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>587819</v>
+        <v>587888</v>
       </c>
       <c r="R20" t="n">
-        <v>6634164</v>
+        <v>6634183</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2917,7 +2912,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2927,7 +2922,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2938,6 +2933,11 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2954,10 +2954,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123251441</v>
+        <v>123249194</v>
       </c>
       <c r="B21" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2989,12 +2989,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3004,17 +3004,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>588163</v>
+        <v>587963</v>
       </c>
       <c r="R21" t="n">
-        <v>6634261</v>
+        <v>6634186</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3085,10 +3085,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123249496</v>
+        <v>123251464</v>
       </c>
       <c r="B22" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3120,12 +3120,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3139,13 +3139,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>588070</v>
+        <v>588142</v>
       </c>
       <c r="R22" t="n">
-        <v>6634198</v>
+        <v>6634249</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3216,10 +3216,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123249372</v>
+        <v>123250606</v>
       </c>
       <c r="B23" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3270,13 +3270,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>588038</v>
+        <v>588109</v>
       </c>
       <c r="R23" t="n">
-        <v>6634200</v>
+        <v>6634191</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3347,10 +3347,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123247980</v>
+        <v>123251441</v>
       </c>
       <c r="B24" t="n">
-        <v>105502</v>
+        <v>98502</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3359,35 +3359,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3397,14 +3397,14 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587889</v>
+        <v>588163</v>
       </c>
       <c r="R24" t="n">
-        <v>6634188</v>
+        <v>6634261</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3461,16 +3461,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Mark/jord på land</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3488,10 +3478,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123251808</v>
+        <v>123247980</v>
       </c>
       <c r="B25" t="n">
-        <v>98396</v>
+        <v>105518</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3500,30 +3490,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3542,13 +3532,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587915</v>
+        <v>587889</v>
       </c>
       <c r="R25" t="n">
-        <v>6634215</v>
+        <v>6634188</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3577,7 +3567,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3587,7 +3577,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3602,6 +3592,16 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3619,10 +3619,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123251012</v>
+        <v>123250437</v>
       </c>
       <c r="B26" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3673,13 +3673,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>588146</v>
+        <v>588103</v>
       </c>
       <c r="R26" t="n">
-        <v>6634204</v>
+        <v>6634221</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3750,10 +3750,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123248025</v>
+        <v>123250520</v>
       </c>
       <c r="B27" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3800,17 +3800,17 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>587890</v>
+        <v>588123</v>
       </c>
       <c r="R27" t="n">
-        <v>6634184</v>
+        <v>6634219</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3881,10 +3881,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123248542</v>
+        <v>123248025</v>
       </c>
       <c r="B28" t="n">
-        <v>57503</v>
+        <v>98502</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3893,46 +3893,55 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kivsta, Kila sn, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>587933</v>
+        <v>587890</v>
       </c>
       <c r="R28" t="n">
-        <v>6634187</v>
+        <v>6634184</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3961,7 +3970,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3971,7 +3980,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3986,26 +3995,6 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4023,10 +4012,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123248683</v>
+        <v>123250354</v>
       </c>
       <c r="B29" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4058,12 +4047,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -4073,14 +4062,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587942</v>
+        <v>588099</v>
       </c>
       <c r="R29" t="n">
-        <v>6634200</v>
+        <v>6634227</v>
       </c>
       <c r="S29" t="n">
         <v>8</v>
@@ -4112,7 +4101,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4122,7 +4111,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4154,10 +4143,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123249452</v>
+        <v>123248683</v>
       </c>
       <c r="B30" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4189,12 +4178,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -4204,17 +4193,17 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>588053</v>
+        <v>587942</v>
       </c>
       <c r="R30" t="n">
         <v>6634200</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4243,7 +4232,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4253,7 +4242,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4285,10 +4274,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123250606</v>
+        <v>123251549</v>
       </c>
       <c r="B31" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4320,7 +4309,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4339,13 +4328,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>588109</v>
+        <v>588114</v>
       </c>
       <c r="R31" t="n">
-        <v>6634191</v>
+        <v>6634233</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4374,7 +4363,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4384,7 +4373,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4416,10 +4405,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123248138</v>
+        <v>123248542</v>
       </c>
       <c r="B32" t="n">
-        <v>105502</v>
+        <v>57506</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4428,55 +4417,46 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Kivsta, Kila sn, Vstm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>587888</v>
+        <v>587933</v>
       </c>
       <c r="R32" t="n">
-        <v>6634183</v>
+        <v>6634187</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4505,7 +4485,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4515,7 +4495,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4530,6 +4510,26 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4550,7 +4550,7 @@
         <v>123251336</v>
       </c>
       <c r="B33" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4678,10 +4678,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123284690</v>
+        <v>123284693</v>
       </c>
       <c r="B34" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>588177</v>
+        <v>588083</v>
       </c>
       <c r="R34" t="n">
-        <v>6634223</v>
+        <v>6634204</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4793,10 +4793,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123284693</v>
+        <v>123284695</v>
       </c>
       <c r="B35" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4828,12 +4828,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>588083</v>
+        <v>588072</v>
       </c>
       <c r="R35" t="n">
-        <v>6634204</v>
+        <v>6634226</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4911,7 +4911,7 @@
         <v>123295537</v>
       </c>
       <c r="B36" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5015,10 +5015,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123284689</v>
+        <v>123284688</v>
       </c>
       <c r="B37" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -5067,10 +5067,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>588176</v>
+        <v>588044</v>
       </c>
       <c r="R37" t="n">
-        <v>6634236</v>
+        <v>6634206</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5133,7 +5133,7 @@
         <v>123284694</v>
       </c>
       <c r="B38" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5245,10 +5245,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123284688</v>
+        <v>123284692</v>
       </c>
       <c r="B39" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5280,12 +5280,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -5297,10 +5297,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>588044</v>
+        <v>588131</v>
       </c>
       <c r="R39" t="n">
-        <v>6634206</v>
+        <v>6634212</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5360,10 +5360,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123284692</v>
+        <v>123284697</v>
       </c>
       <c r="B40" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5412,10 +5412,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>588131</v>
+        <v>587914</v>
       </c>
       <c r="R40" t="n">
-        <v>6634212</v>
+        <v>6634236</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5475,10 +5475,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123284696</v>
+        <v>123284698</v>
       </c>
       <c r="B41" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5527,10 +5527,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>587970</v>
+        <v>587922</v>
       </c>
       <c r="R41" t="n">
-        <v>6634188</v>
+        <v>6634202</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5590,10 +5590,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123284695</v>
+        <v>123284696</v>
       </c>
       <c r="B42" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5625,12 +5625,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -5642,10 +5642,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>588072</v>
+        <v>587970</v>
       </c>
       <c r="R42" t="n">
-        <v>6634226</v>
+        <v>6634188</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5705,10 +5705,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123284698</v>
+        <v>123284689</v>
       </c>
       <c r="B43" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5757,10 +5757,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>587922</v>
+        <v>588176</v>
       </c>
       <c r="R43" t="n">
-        <v>6634202</v>
+        <v>6634236</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5820,10 +5820,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123284697</v>
+        <v>123284690</v>
       </c>
       <c r="B44" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>587914</v>
+        <v>588177</v>
       </c>
       <c r="R44" t="n">
-        <v>6634236</v>
+        <v>6634223</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>

--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -1794,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123249496</v>
+        <v>123247980</v>
       </c>
       <c r="B12" t="n">
-        <v>98502</v>
+        <v>105520</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1806,35 +1806,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1844,17 +1844,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588070</v>
+        <v>587889</v>
       </c>
       <c r="R12" t="n">
-        <v>6634198</v>
+        <v>6634188</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1908,6 +1908,16 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1925,10 +1935,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123249452</v>
+        <v>123249496</v>
       </c>
       <c r="B13" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1960,12 +1970,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1979,13 +1989,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588053</v>
+        <v>588070</v>
       </c>
       <c r="R13" t="n">
-        <v>6634200</v>
+        <v>6634198</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2014,7 +2024,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2024,7 +2034,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2056,10 +2066,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123249094</v>
+        <v>123250520</v>
       </c>
       <c r="B14" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2091,12 +2101,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2106,14 +2116,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>587959</v>
+        <v>588123</v>
       </c>
       <c r="R14" t="n">
-        <v>6634188</v>
+        <v>6634219</v>
       </c>
       <c r="S14" t="n">
         <v>7</v>
@@ -2145,7 +2155,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2155,7 +2165,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2187,10 +2197,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123250725</v>
+        <v>123250354</v>
       </c>
       <c r="B15" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2222,12 +2232,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2241,13 +2251,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>588146</v>
+        <v>588099</v>
       </c>
       <c r="R15" t="n">
-        <v>6634204</v>
+        <v>6634227</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2276,7 +2286,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2286,7 +2296,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2318,10 +2328,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123249372</v>
+        <v>123251464</v>
       </c>
       <c r="B16" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2353,12 +2363,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2372,10 +2382,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>588038</v>
+        <v>588142</v>
       </c>
       <c r="R16" t="n">
-        <v>6634200</v>
+        <v>6634249</v>
       </c>
       <c r="S16" t="n">
         <v>8</v>
@@ -2407,7 +2417,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2417,7 +2427,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2449,10 +2459,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123247723</v>
+        <v>123251808</v>
       </c>
       <c r="B17" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2482,20 +2492,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587819</v>
+        <v>587915</v>
       </c>
       <c r="R17" t="n">
-        <v>6634164</v>
+        <v>6634215</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2524,7 +2548,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2534,7 +2558,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2545,6 +2569,11 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2561,10 +2590,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123251808</v>
+        <v>123251012</v>
       </c>
       <c r="B18" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2596,12 +2625,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2611,17 +2640,17 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587915</v>
+        <v>588146</v>
       </c>
       <c r="R18" t="n">
-        <v>6634215</v>
+        <v>6634204</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2650,7 +2679,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2660,7 +2689,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2692,10 +2721,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123251389</v>
+        <v>123248025</v>
       </c>
       <c r="B19" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2727,12 +2756,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2742,14 +2771,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>588189</v>
+        <v>587890</v>
       </c>
       <c r="R19" t="n">
-        <v>6634246</v>
+        <v>6634184</v>
       </c>
       <c r="S19" t="n">
         <v>6</v>
@@ -2781,7 +2810,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2791,7 +2820,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2823,10 +2852,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123248138</v>
+        <v>123249094</v>
       </c>
       <c r="B20" t="n">
-        <v>105518</v>
+        <v>98504</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2835,35 +2864,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2877,13 +2906,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>587888</v>
+        <v>587959</v>
       </c>
       <c r="R20" t="n">
-        <v>6634183</v>
+        <v>6634188</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2912,7 +2941,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2922,7 +2951,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2954,10 +2983,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123249194</v>
+        <v>123250606</v>
       </c>
       <c r="B21" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2989,7 +3018,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3004,17 +3033,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>587963</v>
+        <v>588109</v>
       </c>
       <c r="R21" t="n">
-        <v>6634186</v>
+        <v>6634191</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3043,7 +3072,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3053,7 +3082,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3085,10 +3114,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123251464</v>
+        <v>123247723</v>
       </c>
       <c r="B22" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3118,34 +3147,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>588142</v>
+        <v>587819</v>
       </c>
       <c r="R22" t="n">
-        <v>6634249</v>
+        <v>6634164</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3174,7 +3189,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3184,7 +3199,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3195,11 +3210,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3216,10 +3226,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123250606</v>
+        <v>123248138</v>
       </c>
       <c r="B23" t="n">
-        <v>98502</v>
+        <v>105520</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3228,30 +3238,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3266,17 +3276,17 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>588109</v>
+        <v>587888</v>
       </c>
       <c r="R23" t="n">
-        <v>6634191</v>
+        <v>6634183</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3305,7 +3315,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3315,7 +3325,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3347,10 +3357,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123251441</v>
+        <v>123249372</v>
       </c>
       <c r="B24" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3382,7 +3392,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3401,10 +3411,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>588163</v>
+        <v>588038</v>
       </c>
       <c r="R24" t="n">
-        <v>6634261</v>
+        <v>6634200</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
@@ -3436,7 +3446,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3446,7 +3456,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3478,10 +3488,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123247980</v>
+        <v>123251441</v>
       </c>
       <c r="B25" t="n">
-        <v>105518</v>
+        <v>98504</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3490,35 +3500,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3528,14 +3538,14 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587889</v>
+        <v>588163</v>
       </c>
       <c r="R25" t="n">
-        <v>6634188</v>
+        <v>6634261</v>
       </c>
       <c r="S25" t="n">
         <v>8</v>
@@ -3567,7 +3577,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3577,7 +3587,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3592,16 +3602,6 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Mark/jord på land</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3619,10 +3619,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123250437</v>
+        <v>123249194</v>
       </c>
       <c r="B26" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3654,12 +3654,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3669,14 +3669,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>588103</v>
+        <v>587963</v>
       </c>
       <c r="R26" t="n">
-        <v>6634221</v>
+        <v>6634186</v>
       </c>
       <c r="S26" t="n">
         <v>7</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3750,10 +3750,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123250520</v>
+        <v>123251549</v>
       </c>
       <c r="B27" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3804,10 +3804,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>588123</v>
+        <v>588114</v>
       </c>
       <c r="R27" t="n">
-        <v>6634219</v>
+        <v>6634233</v>
       </c>
       <c r="S27" t="n">
         <v>7</v>
@@ -3839,7 +3839,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3881,10 +3881,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123248025</v>
+        <v>123249452</v>
       </c>
       <c r="B28" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3931,17 +3931,17 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>587890</v>
+        <v>588053</v>
       </c>
       <c r="R28" t="n">
-        <v>6634184</v>
+        <v>6634200</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4012,10 +4012,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123250354</v>
+        <v>123251389</v>
       </c>
       <c r="B29" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4047,12 +4047,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -4066,13 +4066,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>588099</v>
+        <v>588189</v>
       </c>
       <c r="R29" t="n">
-        <v>6634227</v>
+        <v>6634246</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4143,10 +4143,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123248683</v>
+        <v>123248542</v>
       </c>
       <c r="B30" t="n">
-        <v>98502</v>
+        <v>57507</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4155,55 +4155,46 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Kivsta, Kila sn, Vstm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587942</v>
+        <v>587933</v>
       </c>
       <c r="R30" t="n">
-        <v>6634200</v>
+        <v>6634187</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4232,7 +4223,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4242,7 +4233,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4257,6 +4248,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4274,10 +4285,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123251549</v>
+        <v>123248683</v>
       </c>
       <c r="B31" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4309,12 +4320,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4324,17 +4335,17 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>588114</v>
+        <v>587942</v>
       </c>
       <c r="R31" t="n">
-        <v>6634233</v>
+        <v>6634200</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4363,7 +4374,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4373,7 +4384,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4405,10 +4416,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123248542</v>
+        <v>123250437</v>
       </c>
       <c r="B32" t="n">
-        <v>57506</v>
+        <v>98504</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4417,46 +4428,55 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kivsta, Kila sn, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>587933</v>
+        <v>588103</v>
       </c>
       <c r="R32" t="n">
-        <v>6634187</v>
+        <v>6634221</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4485,7 +4505,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4495,7 +4515,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4510,26 +4530,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4550,7 +4550,7 @@
         <v>123251336</v>
       </c>
       <c r="B33" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4678,10 +4678,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123284693</v>
+        <v>123284688</v>
       </c>
       <c r="B34" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>588083</v>
+        <v>588044</v>
       </c>
       <c r="R34" t="n">
-        <v>6634204</v>
+        <v>6634206</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4793,10 +4793,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123284695</v>
+        <v>123284693</v>
       </c>
       <c r="B35" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4828,12 +4828,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>588072</v>
+        <v>588083</v>
       </c>
       <c r="R35" t="n">
-        <v>6634226</v>
+        <v>6634204</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4908,10 +4908,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123295537</v>
+        <v>123284692</v>
       </c>
       <c r="B36" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4941,8 +4941,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
@@ -4952,13 +4960,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>588070</v>
+        <v>588131</v>
       </c>
       <c r="R36" t="n">
-        <v>6634240</v>
+        <v>6634212</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5015,10 +5023,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123284688</v>
+        <v>123284697</v>
       </c>
       <c r="B37" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5050,12 +5058,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -5067,10 +5075,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>588044</v>
+        <v>587914</v>
       </c>
       <c r="R37" t="n">
-        <v>6634206</v>
+        <v>6634236</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5130,10 +5138,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123284694</v>
+        <v>123284695</v>
       </c>
       <c r="B38" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5165,7 +5173,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5182,10 +5190,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>588076</v>
+        <v>588072</v>
       </c>
       <c r="R38" t="n">
-        <v>6634215</v>
+        <v>6634226</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5245,10 +5253,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123284692</v>
+        <v>123284690</v>
       </c>
       <c r="B39" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5280,7 +5288,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5297,10 +5305,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>588131</v>
+        <v>588177</v>
       </c>
       <c r="R39" t="n">
-        <v>6634212</v>
+        <v>6634223</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5360,10 +5368,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123284697</v>
+        <v>123284696</v>
       </c>
       <c r="B40" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5395,7 +5403,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5412,10 +5420,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>587914</v>
+        <v>587970</v>
       </c>
       <c r="R40" t="n">
-        <v>6634236</v>
+        <v>6634188</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5475,10 +5483,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123284698</v>
+        <v>123295534</v>
       </c>
       <c r="B41" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5510,7 +5518,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5527,13 +5535,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>587922</v>
+        <v>588070</v>
       </c>
       <c r="R41" t="n">
-        <v>6634202</v>
+        <v>6634240</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5590,10 +5598,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123284696</v>
+        <v>123284689</v>
       </c>
       <c r="B42" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5625,7 +5633,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5642,10 +5650,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>587970</v>
+        <v>588176</v>
       </c>
       <c r="R42" t="n">
-        <v>6634188</v>
+        <v>6634236</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5705,10 +5713,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123284689</v>
+        <v>123284698</v>
       </c>
       <c r="B43" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5740,7 +5748,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5757,10 +5765,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>588176</v>
+        <v>587922</v>
       </c>
       <c r="R43" t="n">
-        <v>6634236</v>
+        <v>6634202</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5820,10 +5828,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123284690</v>
+        <v>123284694</v>
       </c>
       <c r="B44" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5855,12 +5863,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -5872,10 +5880,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>588177</v>
+        <v>588076</v>
       </c>
       <c r="R44" t="n">
-        <v>6634223</v>
+        <v>6634215</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>

--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -1794,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123247980</v>
+        <v>123251389</v>
       </c>
       <c r="B12" t="n">
-        <v>105520</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1806,35 +1806,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1844,17 +1844,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587889</v>
+        <v>588189</v>
       </c>
       <c r="R12" t="n">
-        <v>6634188</v>
+        <v>6634246</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1908,16 +1908,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Mark/jord på land</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1935,10 +1925,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123249496</v>
+        <v>123250606</v>
       </c>
       <c r="B13" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1970,12 +1960,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1989,10 +1979,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588070</v>
+        <v>588109</v>
       </c>
       <c r="R13" t="n">
-        <v>6634198</v>
+        <v>6634191</v>
       </c>
       <c r="S13" t="n">
         <v>9</v>
@@ -2024,7 +2014,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2034,7 +2024,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2066,10 +2056,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123250520</v>
+        <v>123250725</v>
       </c>
       <c r="B14" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2101,12 +2091,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2120,13 +2110,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588123</v>
+        <v>588146</v>
       </c>
       <c r="R14" t="n">
-        <v>6634219</v>
+        <v>6634204</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2155,7 +2145,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2165,7 +2155,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2197,10 +2187,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123250354</v>
+        <v>123248542</v>
       </c>
       <c r="B15" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2209,55 +2199,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Kivsta, Kila sn, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>588099</v>
+        <v>587933</v>
       </c>
       <c r="R15" t="n">
-        <v>6634227</v>
+        <v>6634187</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2286,7 +2267,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2296,7 +2277,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2311,6 +2292,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2328,10 +2329,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123251464</v>
+        <v>123247723</v>
       </c>
       <c r="B16" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2361,34 +2362,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>588142</v>
+        <v>587819</v>
       </c>
       <c r="R16" t="n">
-        <v>6634249</v>
+        <v>6634164</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2417,7 +2404,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2427,7 +2414,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2438,11 +2425,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2459,10 +2441,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123251808</v>
+        <v>123249194</v>
       </c>
       <c r="B17" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2494,7 +2476,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2513,13 +2495,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587915</v>
+        <v>587963</v>
       </c>
       <c r="R17" t="n">
-        <v>6634215</v>
+        <v>6634186</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2548,7 +2530,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2558,7 +2540,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2590,10 +2572,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123251012</v>
+        <v>123249496</v>
       </c>
       <c r="B18" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2625,7 +2607,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2644,13 +2626,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>588146</v>
+        <v>588070</v>
       </c>
       <c r="R18" t="n">
-        <v>6634204</v>
+        <v>6634198</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2679,7 +2661,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2689,7 +2671,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2721,10 +2703,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123248025</v>
+        <v>123251808</v>
       </c>
       <c r="B19" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2756,7 +2738,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2775,13 +2757,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587890</v>
+        <v>587915</v>
       </c>
       <c r="R19" t="n">
-        <v>6634184</v>
+        <v>6634215</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2810,7 +2792,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2820,7 +2802,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2852,10 +2834,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123249094</v>
+        <v>123250354</v>
       </c>
       <c r="B20" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2887,12 +2869,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2902,17 +2884,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>587959</v>
+        <v>588099</v>
       </c>
       <c r="R20" t="n">
-        <v>6634188</v>
+        <v>6634227</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2941,7 +2923,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2951,7 +2933,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2983,10 +2965,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123250606</v>
+        <v>123248025</v>
       </c>
       <c r="B21" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3018,7 +3000,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3033,17 +3015,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>588109</v>
+        <v>587890</v>
       </c>
       <c r="R21" t="n">
-        <v>6634191</v>
+        <v>6634184</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3072,7 +3054,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3082,7 +3064,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3114,10 +3096,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123247723</v>
+        <v>123251441</v>
       </c>
       <c r="B22" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3147,20 +3129,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>587819</v>
+        <v>588163</v>
       </c>
       <c r="R22" t="n">
-        <v>6634164</v>
+        <v>6634261</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3189,7 +3185,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3199,7 +3195,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3210,6 +3206,11 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3226,10 +3227,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123248138</v>
+        <v>123248683</v>
       </c>
       <c r="B23" t="n">
-        <v>105520</v>
+        <v>98079</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3238,35 +3239,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3280,10 +3281,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587888</v>
+        <v>587942</v>
       </c>
       <c r="R23" t="n">
-        <v>6634183</v>
+        <v>6634200</v>
       </c>
       <c r="S23" t="n">
         <v>8</v>
@@ -3315,7 +3316,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3325,7 +3326,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3357,10 +3358,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123249372</v>
+        <v>123251549</v>
       </c>
       <c r="B24" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3392,12 +3393,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3411,13 +3412,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>588038</v>
+        <v>588114</v>
       </c>
       <c r="R24" t="n">
-        <v>6634200</v>
+        <v>6634233</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3446,7 +3447,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3456,7 +3457,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3488,10 +3489,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123251441</v>
+        <v>123249372</v>
       </c>
       <c r="B25" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3523,7 +3524,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3542,10 +3543,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>588163</v>
+        <v>588038</v>
       </c>
       <c r="R25" t="n">
-        <v>6634261</v>
+        <v>6634200</v>
       </c>
       <c r="S25" t="n">
         <v>8</v>
@@ -3577,7 +3578,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3587,7 +3588,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3619,10 +3620,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123249194</v>
+        <v>123251464</v>
       </c>
       <c r="B26" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3654,7 +3655,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3669,17 +3670,17 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587963</v>
+        <v>588142</v>
       </c>
       <c r="R26" t="n">
-        <v>6634186</v>
+        <v>6634249</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3708,7 +3709,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3718,7 +3719,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3750,10 +3751,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123251549</v>
+        <v>123249094</v>
       </c>
       <c r="B27" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3785,12 +3786,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3800,14 +3801,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>588114</v>
+        <v>587959</v>
       </c>
       <c r="R27" t="n">
-        <v>6634233</v>
+        <v>6634188</v>
       </c>
       <c r="S27" t="n">
         <v>7</v>
@@ -3839,7 +3840,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3849,7 +3850,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3881,10 +3882,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123249452</v>
+        <v>123250520</v>
       </c>
       <c r="B28" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3916,7 +3917,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3935,10 +3936,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588053</v>
+        <v>588123</v>
       </c>
       <c r="R28" t="n">
-        <v>6634200</v>
+        <v>6634219</v>
       </c>
       <c r="S28" t="n">
         <v>7</v>
@@ -3970,7 +3971,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3980,7 +3981,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4012,10 +4013,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123251389</v>
+        <v>123248138</v>
       </c>
       <c r="B29" t="n">
-        <v>98504</v>
+        <v>105095</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4024,35 +4025,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -4062,17 +4063,17 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>588189</v>
+        <v>587888</v>
       </c>
       <c r="R29" t="n">
-        <v>6634246</v>
+        <v>6634183</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4101,7 +4102,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4111,7 +4112,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4143,10 +4144,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123248542</v>
+        <v>123247980</v>
       </c>
       <c r="B30" t="n">
-        <v>57507</v>
+        <v>105095</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4155,46 +4156,55 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kivsta, Kila sn, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587933</v>
+        <v>587889</v>
       </c>
       <c r="R30" t="n">
-        <v>6634187</v>
+        <v>6634188</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4223,7 +4233,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4233,7 +4243,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4250,24 +4260,14 @@
           <t>Skogsmark</t>
         </is>
       </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Död trädstam</t>
+          <t>Mark/jord på land</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Dead tree stem # Pinus sylvestris</t>
+          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4285,10 +4285,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123248683</v>
+        <v>123249452</v>
       </c>
       <c r="B31" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4320,12 +4320,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4335,17 +4335,17 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>587942</v>
+        <v>588053</v>
       </c>
       <c r="R31" t="n">
         <v>6634200</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4419,7 +4419,7 @@
         <v>123250437</v>
       </c>
       <c r="B32" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>123251336</v>
       </c>
       <c r="B33" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4678,10 +4678,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123284688</v>
+        <v>123284692</v>
       </c>
       <c r="B34" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>588044</v>
+        <v>588131</v>
       </c>
       <c r="R34" t="n">
-        <v>6634206</v>
+        <v>6634212</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4793,10 +4793,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123284693</v>
+        <v>123295537</v>
       </c>
       <c r="B35" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4826,16 +4826,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4845,13 +4837,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>588083</v>
+        <v>588070</v>
       </c>
       <c r="R35" t="n">
-        <v>6634204</v>
+        <v>6634240</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4908,10 +4900,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123284692</v>
+        <v>123284698</v>
       </c>
       <c r="B36" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4943,7 +4935,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4960,10 +4952,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>588131</v>
+        <v>587922</v>
       </c>
       <c r="R36" t="n">
-        <v>6634212</v>
+        <v>6634202</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -5023,10 +5015,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123284697</v>
+        <v>123284695</v>
       </c>
       <c r="B37" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5058,12 +5050,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -5075,10 +5067,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>587914</v>
+        <v>588072</v>
       </c>
       <c r="R37" t="n">
-        <v>6634236</v>
+        <v>6634226</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5138,10 +5130,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123284695</v>
+        <v>123284693</v>
       </c>
       <c r="B38" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5173,12 +5165,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -5190,10 +5182,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>588072</v>
+        <v>588083</v>
       </c>
       <c r="R38" t="n">
-        <v>6634226</v>
+        <v>6634204</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5253,10 +5245,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123284690</v>
+        <v>123284694</v>
       </c>
       <c r="B39" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5288,12 +5280,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -5305,10 +5297,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>588177</v>
+        <v>588076</v>
       </c>
       <c r="R39" t="n">
-        <v>6634223</v>
+        <v>6634215</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5368,10 +5360,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123284696</v>
+        <v>123284688</v>
       </c>
       <c r="B40" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5403,12 +5395,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -5420,10 +5412,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>587970</v>
+        <v>588044</v>
       </c>
       <c r="R40" t="n">
-        <v>6634188</v>
+        <v>6634206</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5483,10 +5475,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123295534</v>
+        <v>123284696</v>
       </c>
       <c r="B41" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5518,7 +5510,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5535,13 +5527,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>588070</v>
+        <v>587970</v>
       </c>
       <c r="R41" t="n">
-        <v>6634240</v>
+        <v>6634188</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5598,10 +5590,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123284689</v>
+        <v>123284697</v>
       </c>
       <c r="B42" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5633,7 +5625,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5650,7 +5642,7 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>588176</v>
+        <v>587914</v>
       </c>
       <c r="R42" t="n">
         <v>6634236</v>
@@ -5713,10 +5705,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123284698</v>
+        <v>123284690</v>
       </c>
       <c r="B43" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5748,7 +5740,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5765,10 +5757,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>587922</v>
+        <v>588177</v>
       </c>
       <c r="R43" t="n">
-        <v>6634202</v>
+        <v>6634223</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5828,10 +5820,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123284694</v>
+        <v>123284689</v>
       </c>
       <c r="B44" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5863,12 +5855,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -5880,10 +5872,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>588076</v>
+        <v>588176</v>
       </c>
       <c r="R44" t="n">
-        <v>6634215</v>
+        <v>6634236</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>

--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -3882,10 +3882,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123250520</v>
+        <v>123248138</v>
       </c>
       <c r="B28" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3894,30 +3894,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3932,17 +3932,17 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588123</v>
+        <v>587888</v>
       </c>
       <c r="R28" t="n">
-        <v>6634219</v>
+        <v>6634183</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4013,10 +4013,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123248138</v>
+        <v>123250520</v>
       </c>
       <c r="B29" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4025,30 +4025,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4063,17 +4063,17 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587888</v>
+        <v>588123</v>
       </c>
       <c r="R29" t="n">
-        <v>6634183</v>
+        <v>6634219</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4144,10 +4144,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123247980</v>
+        <v>123249452</v>
       </c>
       <c r="B30" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4156,25 +4156,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4194,17 +4194,17 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587889</v>
+        <v>588053</v>
       </c>
       <c r="R30" t="n">
-        <v>6634188</v>
+        <v>6634200</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4258,16 +4258,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Mark/jord på land</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4285,7 +4275,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123249452</v>
+        <v>123250437</v>
       </c>
       <c r="B31" t="n">
         <v>98079</v>
@@ -4320,12 +4310,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4339,10 +4329,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>588053</v>
+        <v>588103</v>
       </c>
       <c r="R31" t="n">
-        <v>6634200</v>
+        <v>6634221</v>
       </c>
       <c r="S31" t="n">
         <v>7</v>
@@ -4374,7 +4364,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4384,7 +4374,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4416,10 +4406,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123250437</v>
+        <v>123247980</v>
       </c>
       <c r="B32" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4428,35 +4418,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4466,17 +4456,17 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>588103</v>
+        <v>587889</v>
       </c>
       <c r="R32" t="n">
-        <v>6634221</v>
+        <v>6634188</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4505,7 +4495,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4515,7 +4505,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4530,6 +4520,16 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>

--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -1794,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123251389</v>
+        <v>123247980</v>
       </c>
       <c r="B12" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1806,35 +1806,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1844,17 +1844,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588189</v>
+        <v>587889</v>
       </c>
       <c r="R12" t="n">
-        <v>6634246</v>
+        <v>6634188</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1908,6 +1908,16 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1925,7 +1935,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123250606</v>
+        <v>123251389</v>
       </c>
       <c r="B13" t="n">
         <v>98079</v>
@@ -1960,12 +1970,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1979,13 +1989,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588109</v>
+        <v>588189</v>
       </c>
       <c r="R13" t="n">
-        <v>6634191</v>
+        <v>6634246</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2014,7 +2024,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2024,7 +2034,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2056,7 +2066,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123250725</v>
+        <v>123249194</v>
       </c>
       <c r="B14" t="n">
         <v>98079</v>
@@ -2091,12 +2101,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2106,17 +2116,17 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588146</v>
+        <v>587963</v>
       </c>
       <c r="R14" t="n">
-        <v>6634204</v>
+        <v>6634186</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2145,7 +2155,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2155,7 +2165,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2187,10 +2197,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123248542</v>
+        <v>123251549</v>
       </c>
       <c r="B15" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2199,46 +2209,55 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kivsta, Kila sn, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>587933</v>
+        <v>588114</v>
       </c>
       <c r="R15" t="n">
-        <v>6634187</v>
+        <v>6634233</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2267,7 +2286,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2277,7 +2296,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2292,26 +2311,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2329,7 +2328,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123247723</v>
+        <v>123249452</v>
       </c>
       <c r="B16" t="n">
         <v>98079</v>
@@ -2362,20 +2361,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587819</v>
+        <v>588053</v>
       </c>
       <c r="R16" t="n">
-        <v>6634164</v>
+        <v>6634200</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2404,7 +2417,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2414,7 +2427,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2425,6 +2438,11 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2441,10 +2459,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123249194</v>
+        <v>123248138</v>
       </c>
       <c r="B17" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2453,30 +2471,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2495,13 +2513,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587963</v>
+        <v>587888</v>
       </c>
       <c r="R17" t="n">
-        <v>6634186</v>
+        <v>6634183</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2530,7 +2548,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2540,7 +2558,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2572,7 +2590,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123249496</v>
+        <v>123251464</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2607,12 +2625,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2626,13 +2644,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>588070</v>
+        <v>588142</v>
       </c>
       <c r="R18" t="n">
-        <v>6634198</v>
+        <v>6634249</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2661,7 +2679,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2671,7 +2689,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2703,7 +2721,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123251808</v>
+        <v>123250725</v>
       </c>
       <c r="B19" t="n">
         <v>98079</v>
@@ -2738,12 +2756,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2753,17 +2771,17 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587915</v>
+        <v>588146</v>
       </c>
       <c r="R19" t="n">
-        <v>6634215</v>
+        <v>6634204</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2792,7 +2810,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2802,7 +2820,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2834,7 +2852,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123250354</v>
+        <v>123247723</v>
       </c>
       <c r="B20" t="n">
         <v>98079</v>
@@ -2867,34 +2885,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>588099</v>
+        <v>587819</v>
       </c>
       <c r="R20" t="n">
-        <v>6634227</v>
+        <v>6634164</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2923,7 +2927,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2933,7 +2937,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2944,11 +2948,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2965,7 +2964,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123248025</v>
+        <v>123251441</v>
       </c>
       <c r="B21" t="n">
         <v>98079</v>
@@ -3000,12 +2999,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3015,17 +3014,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>587890</v>
+        <v>588163</v>
       </c>
       <c r="R21" t="n">
-        <v>6634184</v>
+        <v>6634261</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3054,7 +3053,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3064,7 +3063,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3096,7 +3095,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123251441</v>
+        <v>123250606</v>
       </c>
       <c r="B22" t="n">
         <v>98079</v>
@@ -3131,12 +3130,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3150,13 +3149,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>588163</v>
+        <v>588109</v>
       </c>
       <c r="R22" t="n">
-        <v>6634261</v>
+        <v>6634191</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3185,7 +3184,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3195,7 +3194,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3358,7 +3357,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123251549</v>
+        <v>123249496</v>
       </c>
       <c r="B24" t="n">
         <v>98079</v>
@@ -3393,12 +3392,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3412,13 +3411,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>588114</v>
+        <v>588070</v>
       </c>
       <c r="R24" t="n">
-        <v>6634233</v>
+        <v>6634198</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3447,7 +3446,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3457,7 +3456,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3489,7 +3488,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123249372</v>
+        <v>123250520</v>
       </c>
       <c r="B25" t="n">
         <v>98079</v>
@@ -3524,12 +3523,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3543,13 +3542,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>588038</v>
+        <v>588123</v>
       </c>
       <c r="R25" t="n">
-        <v>6634200</v>
+        <v>6634219</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3578,7 +3577,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3588,7 +3587,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3620,7 +3619,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123251464</v>
+        <v>123249094</v>
       </c>
       <c r="B26" t="n">
         <v>98079</v>
@@ -3655,12 +3654,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3670,17 +3669,17 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>588142</v>
+        <v>587959</v>
       </c>
       <c r="R26" t="n">
-        <v>6634249</v>
+        <v>6634188</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3709,7 +3708,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3719,7 +3718,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3751,7 +3750,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123249094</v>
+        <v>123250437</v>
       </c>
       <c r="B27" t="n">
         <v>98079</v>
@@ -3786,7 +3785,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3801,14 +3800,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>587959</v>
+        <v>588103</v>
       </c>
       <c r="R27" t="n">
-        <v>6634188</v>
+        <v>6634221</v>
       </c>
       <c r="S27" t="n">
         <v>7</v>
@@ -3840,7 +3839,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3850,7 +3849,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3882,10 +3881,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123248138</v>
+        <v>123250354</v>
       </c>
       <c r="B28" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3894,30 +3893,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3932,14 +3931,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>587888</v>
+        <v>588099</v>
       </c>
       <c r="R28" t="n">
-        <v>6634183</v>
+        <v>6634227</v>
       </c>
       <c r="S28" t="n">
         <v>8</v>
@@ -3971,7 +3970,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3981,7 +3980,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4013,7 +4012,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123250520</v>
+        <v>123251808</v>
       </c>
       <c r="B29" t="n">
         <v>98079</v>
@@ -4048,7 +4047,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4063,17 +4062,17 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>588123</v>
+        <v>587915</v>
       </c>
       <c r="R29" t="n">
-        <v>6634219</v>
+        <v>6634215</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4102,7 +4101,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4112,7 +4111,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4144,10 +4143,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123249452</v>
+        <v>123248542</v>
       </c>
       <c r="B30" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4156,55 +4155,46 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Kivsta, Kila sn, Vstm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>588053</v>
+        <v>587933</v>
       </c>
       <c r="R30" t="n">
-        <v>6634200</v>
+        <v>6634187</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4233,7 +4223,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4243,7 +4233,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4258,6 +4248,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4275,7 +4285,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123250437</v>
+        <v>123248025</v>
       </c>
       <c r="B31" t="n">
         <v>98079</v>
@@ -4310,12 +4320,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4325,17 +4335,17 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>588103</v>
+        <v>587890</v>
       </c>
       <c r="R31" t="n">
-        <v>6634221</v>
+        <v>6634184</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4364,7 +4374,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4374,7 +4384,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4406,10 +4416,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123247980</v>
+        <v>123249372</v>
       </c>
       <c r="B32" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4418,35 +4428,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4456,14 +4466,14 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>587889</v>
+        <v>588038</v>
       </c>
       <c r="R32" t="n">
-        <v>6634188</v>
+        <v>6634200</v>
       </c>
       <c r="S32" t="n">
         <v>8</v>
@@ -4495,7 +4505,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4505,7 +4515,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4520,16 +4530,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Mark/jord på land</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4678,7 +4678,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123284692</v>
+        <v>123284690</v>
       </c>
       <c r="B34" t="n">
         <v>98079</v>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>588131</v>
+        <v>588177</v>
       </c>
       <c r="R34" t="n">
-        <v>6634212</v>
+        <v>6634223</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4793,7 +4793,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123295537</v>
+        <v>123284693</v>
       </c>
       <c r="B35" t="n">
         <v>98079</v>
@@ -4826,8 +4826,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4837,13 +4845,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>588070</v>
+        <v>588083</v>
       </c>
       <c r="R35" t="n">
-        <v>6634240</v>
+        <v>6634204</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4900,7 +4908,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123284698</v>
+        <v>123284697</v>
       </c>
       <c r="B36" t="n">
         <v>98079</v>
@@ -4935,7 +4943,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4952,10 +4960,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>587922</v>
+        <v>587914</v>
       </c>
       <c r="R36" t="n">
-        <v>6634202</v>
+        <v>6634236</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -5015,7 +5023,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123284695</v>
+        <v>123284698</v>
       </c>
       <c r="B37" t="n">
         <v>98079</v>
@@ -5050,12 +5058,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -5067,10 +5075,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>588072</v>
+        <v>587922</v>
       </c>
       <c r="R37" t="n">
-        <v>6634226</v>
+        <v>6634202</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5130,7 +5138,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123284693</v>
+        <v>123284694</v>
       </c>
       <c r="B38" t="n">
         <v>98079</v>
@@ -5165,12 +5173,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -5182,10 +5190,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>588083</v>
+        <v>588076</v>
       </c>
       <c r="R38" t="n">
-        <v>6634204</v>
+        <v>6634215</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5245,7 +5253,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123284694</v>
+        <v>123295534</v>
       </c>
       <c r="B39" t="n">
         <v>98079</v>
@@ -5280,12 +5288,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -5297,13 +5305,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>588076</v>
+        <v>588070</v>
       </c>
       <c r="R39" t="n">
-        <v>6634215</v>
+        <v>6634240</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5360,7 +5368,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123284688</v>
+        <v>123284696</v>
       </c>
       <c r="B40" t="n">
         <v>98079</v>
@@ -5395,12 +5403,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -5412,10 +5420,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>588044</v>
+        <v>587970</v>
       </c>
       <c r="R40" t="n">
-        <v>6634206</v>
+        <v>6634188</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5475,7 +5483,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123284696</v>
+        <v>123284688</v>
       </c>
       <c r="B41" t="n">
         <v>98079</v>
@@ -5510,12 +5518,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -5527,10 +5535,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>587970</v>
+        <v>588044</v>
       </c>
       <c r="R41" t="n">
-        <v>6634188</v>
+        <v>6634206</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5590,7 +5598,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123284697</v>
+        <v>123284689</v>
       </c>
       <c r="B42" t="n">
         <v>98079</v>
@@ -5625,7 +5633,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5642,7 +5650,7 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>587914</v>
+        <v>588176</v>
       </c>
       <c r="R42" t="n">
         <v>6634236</v>
@@ -5705,7 +5713,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123284690</v>
+        <v>123284692</v>
       </c>
       <c r="B43" t="n">
         <v>98079</v>
@@ -5740,7 +5748,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5757,10 +5765,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>588177</v>
+        <v>588131</v>
       </c>
       <c r="R43" t="n">
-        <v>6634223</v>
+        <v>6634212</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5820,7 +5828,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123284689</v>
+        <v>123284695</v>
       </c>
       <c r="B44" t="n">
         <v>98079</v>
@@ -5855,12 +5863,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -5872,10 +5880,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>588176</v>
+        <v>588072</v>
       </c>
       <c r="R44" t="n">
-        <v>6634236</v>
+        <v>6634226</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>

--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -4678,7 +4678,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123284690</v>
+        <v>123284693</v>
       </c>
       <c r="B34" t="n">
         <v>98079</v>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>588177</v>
+        <v>588083</v>
       </c>
       <c r="R34" t="n">
-        <v>6634223</v>
+        <v>6634204</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4793,7 +4793,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123284693</v>
+        <v>123284695</v>
       </c>
       <c r="B35" t="n">
         <v>98079</v>
@@ -4828,12 +4828,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>588083</v>
+        <v>588072</v>
       </c>
       <c r="R35" t="n">
-        <v>6634204</v>
+        <v>6634226</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -5023,7 +5023,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123284698</v>
+        <v>123284689</v>
       </c>
       <c r="B37" t="n">
         <v>98079</v>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>587922</v>
+        <v>588176</v>
       </c>
       <c r="R37" t="n">
-        <v>6634202</v>
+        <v>6634236</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5253,7 +5253,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123295534</v>
+        <v>123284696</v>
       </c>
       <c r="B39" t="n">
         <v>98079</v>
@@ -5288,7 +5288,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5305,13 +5305,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>588070</v>
+        <v>587970</v>
       </c>
       <c r="R39" t="n">
-        <v>6634240</v>
+        <v>6634188</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123284696</v>
+        <v>123284698</v>
       </c>
       <c r="B40" t="n">
         <v>98079</v>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5420,10 +5420,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>587970</v>
+        <v>587922</v>
       </c>
       <c r="R40" t="n">
-        <v>6634188</v>
+        <v>6634202</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5483,7 +5483,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123284688</v>
+        <v>123284692</v>
       </c>
       <c r="B41" t="n">
         <v>98079</v>
@@ -5518,12 +5518,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -5535,10 +5535,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>588044</v>
+        <v>588131</v>
       </c>
       <c r="R41" t="n">
-        <v>6634206</v>
+        <v>6634212</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5598,7 +5598,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123284689</v>
+        <v>123284690</v>
       </c>
       <c r="B42" t="n">
         <v>98079</v>
@@ -5633,7 +5633,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5650,10 +5650,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>588176</v>
+        <v>588177</v>
       </c>
       <c r="R42" t="n">
-        <v>6634236</v>
+        <v>6634223</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5713,7 +5713,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123284692</v>
+        <v>123295537</v>
       </c>
       <c r="B43" t="n">
         <v>98079</v>
@@ -5746,16 +5746,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
@@ -5765,13 +5757,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>588131</v>
+        <v>588070</v>
       </c>
       <c r="R43" t="n">
-        <v>6634212</v>
+        <v>6634240</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5828,7 +5820,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123284695</v>
+        <v>123284688</v>
       </c>
       <c r="B44" t="n">
         <v>98079</v>
@@ -5863,7 +5855,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5880,10 +5872,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>588072</v>
+        <v>588044</v>
       </c>
       <c r="R44" t="n">
-        <v>6634226</v>
+        <v>6634206</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>

--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -4678,7 +4678,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123284693</v>
+        <v>123284692</v>
       </c>
       <c r="B34" t="n">
         <v>98079</v>
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>588083</v>
+        <v>588131</v>
       </c>
       <c r="R34" t="n">
-        <v>6634204</v>
+        <v>6634212</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4793,7 +4793,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123284695</v>
+        <v>123284693</v>
       </c>
       <c r="B35" t="n">
         <v>98079</v>
@@ -4828,12 +4828,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>588072</v>
+        <v>588083</v>
       </c>
       <c r="R35" t="n">
-        <v>6634226</v>
+        <v>6634204</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -5023,7 +5023,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123284689</v>
+        <v>123284690</v>
       </c>
       <c r="B37" t="n">
         <v>98079</v>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>588176</v>
+        <v>588177</v>
       </c>
       <c r="R37" t="n">
-        <v>6634236</v>
+        <v>6634223</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5138,7 +5138,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123284694</v>
+        <v>123284688</v>
       </c>
       <c r="B38" t="n">
         <v>98079</v>
@@ -5173,7 +5173,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5190,10 +5190,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>588076</v>
+        <v>588044</v>
       </c>
       <c r="R38" t="n">
-        <v>6634215</v>
+        <v>6634206</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5253,7 +5253,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123284696</v>
+        <v>123284695</v>
       </c>
       <c r="B39" t="n">
         <v>98079</v>
@@ -5288,12 +5288,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -5305,10 +5305,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>587970</v>
+        <v>588072</v>
       </c>
       <c r="R39" t="n">
-        <v>6634188</v>
+        <v>6634226</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5483,7 +5483,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123284692</v>
+        <v>123284696</v>
       </c>
       <c r="B41" t="n">
         <v>98079</v>
@@ -5535,10 +5535,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>588131</v>
+        <v>587970</v>
       </c>
       <c r="R41" t="n">
-        <v>6634212</v>
+        <v>6634188</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5598,7 +5598,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123284690</v>
+        <v>123284689</v>
       </c>
       <c r="B42" t="n">
         <v>98079</v>
@@ -5633,7 +5633,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5650,10 +5650,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>588177</v>
+        <v>588176</v>
       </c>
       <c r="R42" t="n">
-        <v>6634223</v>
+        <v>6634236</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5713,7 +5713,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123295537</v>
+        <v>123295534</v>
       </c>
       <c r="B43" t="n">
         <v>98079</v>
@@ -5746,8 +5746,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
@@ -5820,7 +5828,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123284688</v>
+        <v>123284694</v>
       </c>
       <c r="B44" t="n">
         <v>98079</v>
@@ -5855,7 +5863,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5872,10 +5880,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>588044</v>
+        <v>588076</v>
       </c>
       <c r="R44" t="n">
-        <v>6634206</v>
+        <v>6634215</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>

--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -5946,7 +5946,7 @@
         <v>126908918</v>
       </c>
       <c r="B45" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>126908559</v>
       </c>
       <c r="B46" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -5946,7 +5946,7 @@
         <v>126908918</v>
       </c>
       <c r="B45" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>126908559</v>
       </c>
       <c r="B46" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -5946,7 +5946,7 @@
         <v>126908918</v>
       </c>
       <c r="B45" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>126908559</v>
       </c>
       <c r="B46" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -5946,7 +5946,7 @@
         <v>126908918</v>
       </c>
       <c r="B45" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>126908559</v>
       </c>
       <c r="B46" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -5946,7 +5946,7 @@
         <v>126908918</v>
       </c>
       <c r="B45" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>126908559</v>
       </c>
       <c r="B46" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -5946,7 +5946,7 @@
         <v>126908918</v>
       </c>
       <c r="B45" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>126908559</v>
       </c>
       <c r="B46" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -5946,7 +5946,7 @@
         <v>126908918</v>
       </c>
       <c r="B45" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>126908559</v>
       </c>
       <c r="B46" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -4146,7 +4146,7 @@
         <v>123248542</v>
       </c>
       <c r="B30" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -4146,7 +4146,7 @@
         <v>123248542</v>
       </c>
       <c r="B30" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -4146,7 +4146,7 @@
         <v>123248542</v>
       </c>
       <c r="B30" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -4146,7 +4146,7 @@
         <v>123248542</v>
       </c>
       <c r="B30" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -4146,7 +4146,7 @@
         <v>123248542</v>
       </c>
       <c r="B30" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114569955</v>
+        <v>114571379</v>
       </c>
       <c r="B2" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Munga-Horndal, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588158</v>
+        <v>588157</v>
       </c>
       <c r="R2" t="n">
-        <v>6634256</v>
+        <v>6634259</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -767,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,61 +772,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114569957</v>
+        <v>123248542</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Munga-Horndal, Vstm</t>
+          <t>Kivsta, Kila sn, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588185</v>
+        <v>587933</v>
       </c>
       <c r="R3" t="n">
-        <v>6634256</v>
+        <v>6634187</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,94 +842,130 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mårten Nilsson</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114569950</v>
+        <v>96066473</v>
       </c>
       <c r="B4" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Munga-Horndal, Vstm</t>
+          <t>Kivsta, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588061</v>
+        <v>588251</v>
       </c>
       <c r="R4" t="n">
-        <v>6634213</v>
+        <v>6634222</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,12 +989,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2021-08-24</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2021-08-24</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,34 +1013,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mårten Nilsson</t>
+          <t>Anders Hellkvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Anders Hellkvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114569961</v>
+        <v>114569945</v>
       </c>
       <c r="B5" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,7 +1061,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1056,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588193</v>
+        <v>587899</v>
       </c>
       <c r="R5" t="n">
-        <v>6634223</v>
+        <v>6634220</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,15 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114569959</v>
+        <v>114569947</v>
       </c>
       <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,7 +1167,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1167,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588172</v>
+        <v>588043</v>
       </c>
       <c r="R6" t="n">
-        <v>6634247</v>
+        <v>6634189</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,15 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114571379</v>
+        <v>114569950</v>
       </c>
       <c r="B7" t="n">
-        <v>91028</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,34 +1254,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>67</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Munga-Horndal, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588157</v>
+        <v>588061</v>
       </c>
       <c r="R7" t="n">
-        <v>6634259</v>
+        <v>6634213</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,6 +1330,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1335,12 +1352,7 @@
         <v>114569953</v>
       </c>
       <c r="B8" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,15 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114569947</v>
+        <v>114569955</v>
       </c>
       <c r="B9" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,7 +1485,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1491,10 +1498,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588043</v>
+        <v>588158</v>
       </c>
       <c r="R9" t="n">
-        <v>6634189</v>
+        <v>6634256</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,15 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114569945</v>
+        <v>114569957</v>
       </c>
       <c r="B10" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1589,7 +1591,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1602,10 +1604,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587899</v>
+        <v>588185</v>
       </c>
       <c r="R10" t="n">
-        <v>6634220</v>
+        <v>6634256</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,15 +1667,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115005904</v>
+        <v>114569959</v>
       </c>
       <c r="B11" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1700,30 +1697,26 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kivsta, 900 m ONO om (knärot), Vstm</t>
+          <t>Munga-Horndal, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588062</v>
+        <v>588172</v>
       </c>
       <c r="R11" t="n">
-        <v>6634213</v>
+        <v>6634247</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1745,11 +1738,6 @@
           <t>Kila</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>U-Sal-0869</t>
-        </is>
-      </c>
       <c r="Y11" t="inlineStr">
         <is>
           <t>2023-07-18</t>
@@ -1758,11 +1746,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>X: (10), 10 ex, A: 934/417 (10), 20 ex, B: 928/450 (10), 10 ex, egentligen är FV (30)</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1778,7 +1761,7 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Mårten Nilsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -1786,75 +1769,60 @@
           <t>Ward Tamsyn</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige, Inventering längs blivande kraftledning Munga-Horndal</t>
-        </is>
-      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123247980</v>
+        <v>114569961</v>
       </c>
       <c r="B12" t="n">
-        <v>105095</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Munga-Horndal, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587889</v>
+        <v>588193</v>
       </c>
       <c r="R12" t="n">
-        <v>6634188</v>
+        <v>6634223</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1878,22 +1846,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:21</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:21</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,48 +1860,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Mark/jord på land</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Ground/soil on land</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Mårten Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123251389</v>
+        <v>115005904</v>
       </c>
       <c r="B13" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1970,32 +1909,30 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Kivsta, 900 m ONO om (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588189</v>
+        <v>588062</v>
       </c>
       <c r="R13" t="n">
-        <v>6634246</v>
+        <v>6634213</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2017,24 +1954,24 @@
           <t>Kila</t>
         </is>
       </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>U-Sal-0869</t>
+        </is>
+      </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:06</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:06</t>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>X: (10), 10 ex, A: 934/417 (10), 20 ex, B: 928/450 (10), 10 ex, egentligen är FV (30)</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2043,38 +1980,33 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Bo Eriksson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige, Inventering längs blivande kraftledning Munga-Horndal</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123249194</v>
+        <v>123247723</v>
       </c>
       <c r="B14" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2099,34 +2031,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>587963</v>
+        <v>587819</v>
       </c>
       <c r="R14" t="n">
-        <v>6634186</v>
+        <v>6634164</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2155,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2165,7 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2176,11 +2094,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2197,15 +2110,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123251549</v>
+        <v>123248025</v>
       </c>
       <c r="B15" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2232,7 +2140,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2247,17 +2155,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>588114</v>
+        <v>587890</v>
       </c>
       <c r="R15" t="n">
-        <v>6634233</v>
+        <v>6634184</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2286,7 +2194,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2296,7 +2204,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2328,15 +2236,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123249452</v>
+        <v>123248683</v>
       </c>
       <c r="B16" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,12 +2266,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2378,17 +2281,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>588053</v>
+        <v>587942</v>
       </c>
       <c r="R16" t="n">
         <v>6634200</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2417,7 +2320,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2427,7 +2330,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2459,47 +2362,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123248138</v>
+        <v>123249094</v>
       </c>
       <c r="B17" t="n">
-        <v>105095</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2513,13 +2411,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587888</v>
+        <v>587959</v>
       </c>
       <c r="R17" t="n">
-        <v>6634183</v>
+        <v>6634188</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2548,7 +2446,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2558,7 +2456,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2590,15 +2488,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123251464</v>
+        <v>123249194</v>
       </c>
       <c r="B18" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2625,7 +2518,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2640,17 +2533,17 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>588142</v>
+        <v>587963</v>
       </c>
       <c r="R18" t="n">
-        <v>6634249</v>
+        <v>6634186</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2679,7 +2572,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2689,7 +2582,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2721,15 +2614,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123250725</v>
+        <v>123249372</v>
       </c>
       <c r="B19" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2756,7 +2644,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2775,13 +2663,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>588146</v>
+        <v>588038</v>
       </c>
       <c r="R19" t="n">
-        <v>6634204</v>
+        <v>6634200</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2810,7 +2698,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2820,7 +2708,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2852,15 +2740,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123247723</v>
+        <v>123249452</v>
       </c>
       <c r="B20" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2885,20 +2768,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>587819</v>
+        <v>588053</v>
       </c>
       <c r="R20" t="n">
-        <v>6634164</v>
+        <v>6634200</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2927,7 +2824,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2937,7 +2834,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2948,6 +2845,11 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2964,15 +2866,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123251441</v>
+        <v>123249496</v>
       </c>
       <c r="B21" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2999,7 +2896,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3018,13 +2915,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>588163</v>
+        <v>588070</v>
       </c>
       <c r="R21" t="n">
-        <v>6634261</v>
+        <v>6634198</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3053,7 +2950,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3063,7 +2960,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3095,15 +2992,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123250606</v>
+        <v>123250354</v>
       </c>
       <c r="B22" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3149,13 +3041,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>588109</v>
+        <v>588099</v>
       </c>
       <c r="R22" t="n">
-        <v>6634191</v>
+        <v>6634227</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3184,7 +3076,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3194,7 +3086,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3226,15 +3118,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123248683</v>
+        <v>123250437</v>
       </c>
       <c r="B23" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3261,7 +3148,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3276,17 +3163,17 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587942</v>
+        <v>588103</v>
       </c>
       <c r="R23" t="n">
-        <v>6634200</v>
+        <v>6634221</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3315,7 +3202,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3325,7 +3212,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3357,15 +3244,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123249496</v>
+        <v>123250520</v>
       </c>
       <c r="B24" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3392,12 +3274,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3411,13 +3293,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>588070</v>
+        <v>588123</v>
       </c>
       <c r="R24" t="n">
-        <v>6634198</v>
+        <v>6634219</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3446,7 +3328,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3456,7 +3338,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3488,15 +3370,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123250520</v>
+        <v>123250606</v>
       </c>
       <c r="B25" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3523,7 +3400,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3542,13 +3419,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>588123</v>
+        <v>588109</v>
       </c>
       <c r="R25" t="n">
-        <v>6634219</v>
+        <v>6634191</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3577,7 +3454,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3587,7 +3464,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3619,15 +3496,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123249094</v>
+        <v>123250725</v>
       </c>
       <c r="B26" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3654,7 +3526,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3669,17 +3541,17 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587959</v>
+        <v>588146</v>
       </c>
       <c r="R26" t="n">
-        <v>6634188</v>
+        <v>6634204</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3708,7 +3580,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3718,7 +3590,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3750,15 +3622,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123250437</v>
+        <v>123251336</v>
       </c>
       <c r="B27" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3785,7 +3652,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3804,13 +3671,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>588103</v>
+        <v>588190</v>
       </c>
       <c r="R27" t="n">
-        <v>6634221</v>
+        <v>6634249</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3839,7 +3706,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3849,7 +3716,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3881,15 +3748,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123250354</v>
+        <v>123251389</v>
       </c>
       <c r="B28" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3916,12 +3778,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3935,13 +3797,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588099</v>
+        <v>588189</v>
       </c>
       <c r="R28" t="n">
-        <v>6634227</v>
+        <v>6634246</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3970,7 +3832,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3980,7 +3842,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4012,15 +3874,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123251808</v>
+        <v>123251441</v>
       </c>
       <c r="B29" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4047,12 +3904,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -4062,17 +3919,17 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587915</v>
+        <v>588163</v>
       </c>
       <c r="R29" t="n">
-        <v>6634215</v>
+        <v>6634261</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4101,7 +3958,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4111,7 +3968,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4143,53 +4000,62 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123248542</v>
+        <v>123251464</v>
       </c>
       <c r="B30" t="n">
-        <v>57889</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kivsta, Kila sn, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587933</v>
+        <v>588142</v>
       </c>
       <c r="R30" t="n">
-        <v>6634187</v>
+        <v>6634249</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4218,7 +4084,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4228,14 +4094,14 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="b">
         <v>0</v>
@@ -4243,26 +4109,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4280,15 +4126,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123248025</v>
+        <v>123251549</v>
       </c>
       <c r="B31" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4315,7 +4156,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4330,17 +4171,17 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Norrängsberget, Norrängsberget, Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>587890</v>
+        <v>588114</v>
       </c>
       <c r="R31" t="n">
-        <v>6634184</v>
+        <v>6634233</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4369,7 +4210,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4379,7 +4220,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4411,15 +4252,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123249372</v>
+        <v>123251808</v>
       </c>
       <c r="B32" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4446,12 +4282,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4461,17 +4297,17 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>588038</v>
+        <v>587915</v>
       </c>
       <c r="R32" t="n">
-        <v>6634200</v>
+        <v>6634215</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4500,7 +4336,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4510,7 +4346,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4542,15 +4378,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123251336</v>
+        <v>123284688</v>
       </c>
       <c r="B33" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4577,7 +4408,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4585,24 +4416,22 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Överstmossen, Överstmossen, Vstm</t>
+          <t>O Kivsta, Vstm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>588190</v>
+        <v>588044</v>
       </c>
       <c r="R33" t="n">
-        <v>6634249</v>
+        <v>6634206</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4629,59 +4458,40 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123284692</v>
+        <v>123284689</v>
       </c>
       <c r="B34" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4708,7 +4518,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4725,10 +4535,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>588131</v>
+        <v>588176</v>
       </c>
       <c r="R34" t="n">
-        <v>6634212</v>
+        <v>6634236</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4788,15 +4598,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123284693</v>
+        <v>123284690</v>
       </c>
       <c r="B35" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4823,7 +4628,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4840,10 +4645,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>588083</v>
+        <v>588177</v>
       </c>
       <c r="R35" t="n">
-        <v>6634204</v>
+        <v>6634223</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4903,15 +4708,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123284697</v>
+        <v>123284692</v>
       </c>
       <c r="B36" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4938,7 +4738,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4955,10 +4755,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>587914</v>
+        <v>588131</v>
       </c>
       <c r="R36" t="n">
-        <v>6634236</v>
+        <v>6634212</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -5018,15 +4818,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123284690</v>
+        <v>123284693</v>
       </c>
       <c r="B37" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5053,7 +4848,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5070,10 +4865,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>588177</v>
+        <v>588083</v>
       </c>
       <c r="R37" t="n">
-        <v>6634223</v>
+        <v>6634204</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5133,15 +4928,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123284688</v>
+        <v>123284694</v>
       </c>
       <c r="B38" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5168,7 +4958,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5185,10 +4975,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>588044</v>
+        <v>588076</v>
       </c>
       <c r="R38" t="n">
-        <v>6634206</v>
+        <v>6634215</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5251,12 +5041,7 @@
         <v>123284695</v>
       </c>
       <c r="B39" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5363,15 +5148,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123284698</v>
+        <v>123284696</v>
       </c>
       <c r="B40" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5398,7 +5178,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5415,10 +5195,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>587922</v>
+        <v>587970</v>
       </c>
       <c r="R40" t="n">
-        <v>6634202</v>
+        <v>6634188</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5478,15 +5258,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123284696</v>
+        <v>123284697</v>
       </c>
       <c r="B41" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5513,7 +5288,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5530,10 +5305,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>587970</v>
+        <v>587914</v>
       </c>
       <c r="R41" t="n">
-        <v>6634188</v>
+        <v>6634236</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5593,15 +5368,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123284689</v>
+        <v>123284698</v>
       </c>
       <c r="B42" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5628,7 +5398,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5645,10 +5415,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>588176</v>
+        <v>587922</v>
       </c>
       <c r="R42" t="n">
-        <v>6634236</v>
+        <v>6634202</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5711,12 +5481,7 @@
         <v>123295534</v>
       </c>
       <c r="B43" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5823,15 +5588,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123284694</v>
+        <v>126908559</v>
       </c>
       <c r="B44" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5858,7 +5618,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5866,22 +5626,26 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>O Kivsta, Vstm</t>
+          <t>Överstmossen (knärot3), Vstm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>588076</v>
+        <v>588123</v>
       </c>
       <c r="R44" t="n">
-        <v>6634215</v>
+        <v>6634220</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5903,6 +5667,11 @@
           <t>Kila</t>
         </is>
       </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>U-Sal-1155</t>
+        </is>
+      </c>
       <c r="Y44" t="inlineStr">
         <is>
           <t>2025-03-16</t>
@@ -5911,6 +5680,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>X (7) 1 pl A 006/460(7): 5 pl, B:42995/447 (7) 12 m2 ,    C 42991/453(8), 10 pl, D 001/4177(9):10 pl, E 037/430(6):20 m2. Foton OK</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5926,22 +5700,26 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Bo Eriksson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>126908918</v>
       </c>
       <c r="B45" t="n">
-        <v>98450</v>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5985,7 +5763,7 @@
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Överstmossen 5 (knärot), Vstm</t>
+          <t>Överstmossen (knärot5), Vstm</t>
         </is>
       </c>
       <c r="Q45" t="n">
@@ -6066,42 +5844,42 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126908559</v>
+        <v>123247980</v>
       </c>
       <c r="B46" t="n">
-        <v>98450</v>
+        <v>106244</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -6109,21 +5887,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Överstmossen 3 (knärot), Vstm</t>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>588123</v>
+        <v>587889</v>
       </c>
       <c r="R46" t="n">
-        <v>6634220</v>
+        <v>6634188</v>
       </c>
       <c r="S46" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6145,24 +5921,24 @@
           <t>Kila</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>U-Sal-1155</t>
-        </is>
-      </c>
       <c r="Y46" t="inlineStr">
         <is>
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>X (7) 1 pl A 006/460(7): 5 pl, B:42995/447 (7) 12 m2 ,    C 42991/453(8), 10 pl, D 001/4177(9):10 pl, E 037/430(6):20 m2. Foton OK</t>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6171,14 +5947,28 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
@@ -6186,11 +5976,133 @@
           <t>Lars Bohlin</t>
         </is>
       </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>123248138</v>
+      </c>
+      <c r="B47" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Norrängsberget, Norrängsberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>587888</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6634183</v>
+      </c>
+      <c r="S47" t="n">
+        <v>8</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34752-2023 artfynd.xlsx
+++ b/artfynd/A 34752-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114571379</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123248542</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1028,6 +1043,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96066473</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1134,6 +1154,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114569945</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1240,6 +1265,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114569947</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1346,6 +1376,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114569950</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1452,6 +1487,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114569953</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1558,6 +1598,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114569955</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1664,6 +1709,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114569957</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1770,6 +1820,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114569959</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1876,6 +1931,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114569961</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2000,6 +2060,11 @@
           <t>Floraväkteri Sverige, Inventering längs blivande kraftledning Munga-Horndal</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115005904</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2107,6 +2172,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123247723</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2233,6 +2303,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123248025</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2359,6 +2434,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123248683</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2485,6 +2565,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123249094</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2611,6 +2696,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123249194</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2737,6 +2827,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123249372</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2863,6 +2958,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123249452</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2989,6 +3089,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123249496</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3115,6 +3220,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123250354</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3241,6 +3351,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123250437</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3367,6 +3482,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123250520</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3493,6 +3613,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123250606</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3619,6 +3744,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123250725</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3745,6 +3875,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123251336</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3871,6 +4006,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123251389</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3997,6 +4137,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123251441</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4123,6 +4268,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123251464</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4249,6 +4399,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123251549</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4375,6 +4530,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123251808</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4485,6 +4645,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123284688</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4595,6 +4760,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123284689</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4705,6 +4875,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123284690</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4815,6 +4990,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123284692</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4925,6 +5105,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123284693</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5035,6 +5220,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123284694</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5145,6 +5335,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123284695</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5255,6 +5450,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123284696</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5365,6 +5565,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123284697</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5475,6 +5680,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123284698</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5585,6 +5795,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123295534</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5713,6 +5928,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126908559</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5841,6 +6061,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126908918</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5977,6 +6202,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123247980</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6103,8 +6333,61 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123248138</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>